--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BE2E18-B37F-42A8-ABB7-A6DAEB70A3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5910E270-C306-413C-941C-CAB0BDAEB35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2111"/>
+  <dimension ref="A1:T2181"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -37228,6 +37228,1196 @@
         <v>11</v>
       </c>
     </row>
+    <row r="2112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2112">
+        <v>106</v>
+      </c>
+      <c r="B2112" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2112">
+        <v>1</v>
+      </c>
+      <c r="D2112">
+        <v>6041</v>
+      </c>
+      <c r="E2112">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2113">
+        <v>106</v>
+      </c>
+      <c r="B2113" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2113">
+        <v>1</v>
+      </c>
+      <c r="D2113">
+        <v>2648</v>
+      </c>
+      <c r="E2113">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2114">
+        <v>106</v>
+      </c>
+      <c r="B2114" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2114">
+        <v>1</v>
+      </c>
+      <c r="D2114">
+        <v>11</v>
+      </c>
+      <c r="E2114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2115">
+        <v>106</v>
+      </c>
+      <c r="B2115" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2115">
+        <v>1</v>
+      </c>
+      <c r="D2115">
+        <v>9800</v>
+      </c>
+      <c r="E2115">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2116">
+        <v>106</v>
+      </c>
+      <c r="B2116" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2116">
+        <v>1</v>
+      </c>
+      <c r="D2116">
+        <v>1453</v>
+      </c>
+      <c r="E2116">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2117">
+        <v>106</v>
+      </c>
+      <c r="B2117" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2117">
+        <v>1</v>
+      </c>
+      <c r="D2117">
+        <v>8312</v>
+      </c>
+      <c r="E2117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2118">
+        <v>106</v>
+      </c>
+      <c r="B2118" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2118">
+        <v>1</v>
+      </c>
+      <c r="D2118">
+        <v>5850</v>
+      </c>
+      <c r="E2118">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2119">
+        <v>106</v>
+      </c>
+      <c r="B2119" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2119">
+        <v>1</v>
+      </c>
+      <c r="D2119">
+        <v>1371</v>
+      </c>
+      <c r="E2119">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2120">
+        <v>106</v>
+      </c>
+      <c r="B2120" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2120">
+        <v>1</v>
+      </c>
+      <c r="D2120">
+        <v>1076</v>
+      </c>
+      <c r="E2120">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2121">
+        <v>106</v>
+      </c>
+      <c r="B2121" s="10">
+        <v>46025</v>
+      </c>
+      <c r="C2121">
+        <v>1</v>
+      </c>
+      <c r="D2121">
+        <v>6085</v>
+      </c>
+      <c r="E2121">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2122">
+        <v>107</v>
+      </c>
+      <c r="B2122" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2122">
+        <v>0</v>
+      </c>
+      <c r="D2122">
+        <v>1315</v>
+      </c>
+      <c r="E2122">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2123">
+        <v>107</v>
+      </c>
+      <c r="B2123" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2123">
+        <v>0</v>
+      </c>
+      <c r="D2123">
+        <v>1354</v>
+      </c>
+      <c r="E2123">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2124">
+        <v>107</v>
+      </c>
+      <c r="B2124" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2124">
+        <v>0</v>
+      </c>
+      <c r="D2124">
+        <v>9249</v>
+      </c>
+      <c r="E2124">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2125">
+        <v>107</v>
+      </c>
+      <c r="B2125" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2125">
+        <v>0</v>
+      </c>
+      <c r="D2125">
+        <v>1093</v>
+      </c>
+      <c r="E2125">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2126">
+        <v>107</v>
+      </c>
+      <c r="B2126" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2126">
+        <v>0</v>
+      </c>
+      <c r="D2126">
+        <v>8614</v>
+      </c>
+      <c r="E2126">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2127">
+        <v>107</v>
+      </c>
+      <c r="B2127" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2127">
+        <v>0</v>
+      </c>
+      <c r="D2127">
+        <v>2191</v>
+      </c>
+      <c r="E2127">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2128">
+        <v>107</v>
+      </c>
+      <c r="B2128" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2128">
+        <v>0</v>
+      </c>
+      <c r="D2128">
+        <v>8509</v>
+      </c>
+      <c r="E2128">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2129">
+        <v>107</v>
+      </c>
+      <c r="B2129" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2129">
+        <v>0</v>
+      </c>
+      <c r="D2129">
+        <v>6742</v>
+      </c>
+      <c r="E2129">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2130">
+        <v>107</v>
+      </c>
+      <c r="B2130" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2130">
+        <v>0</v>
+      </c>
+      <c r="D2130">
+        <v>7639</v>
+      </c>
+      <c r="E2130">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2131">
+        <v>107</v>
+      </c>
+      <c r="B2131" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2131">
+        <v>0</v>
+      </c>
+      <c r="D2131">
+        <v>1941</v>
+      </c>
+      <c r="E2131">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2132">
+        <v>107</v>
+      </c>
+      <c r="B2132" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2132">
+        <v>1</v>
+      </c>
+      <c r="D2132">
+        <v>3082</v>
+      </c>
+      <c r="E2132">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2133">
+        <v>107</v>
+      </c>
+      <c r="B2133" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2133">
+        <v>1</v>
+      </c>
+      <c r="D2133">
+        <v>6086</v>
+      </c>
+      <c r="E2133">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2134">
+        <v>107</v>
+      </c>
+      <c r="B2134" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2134">
+        <v>1</v>
+      </c>
+      <c r="D2134">
+        <v>5476</v>
+      </c>
+      <c r="E2134">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2135">
+        <v>107</v>
+      </c>
+      <c r="B2135" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2135">
+        <v>1</v>
+      </c>
+      <c r="D2135">
+        <v>4450</v>
+      </c>
+      <c r="E2135">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2136">
+        <v>107</v>
+      </c>
+      <c r="B2136" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2136">
+        <v>1</v>
+      </c>
+      <c r="D2136">
+        <v>2724</v>
+      </c>
+      <c r="E2136">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2137">
+        <v>107</v>
+      </c>
+      <c r="B2137" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2137">
+        <v>1</v>
+      </c>
+      <c r="D2137">
+        <v>630</v>
+      </c>
+      <c r="E2137">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2138">
+        <v>107</v>
+      </c>
+      <c r="B2138" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2138">
+        <v>1</v>
+      </c>
+      <c r="D2138">
+        <v>2686</v>
+      </c>
+      <c r="E2138">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2139">
+        <v>107</v>
+      </c>
+      <c r="B2139" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2139">
+        <v>1</v>
+      </c>
+      <c r="D2139">
+        <v>8318</v>
+      </c>
+      <c r="E2139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2140">
+        <v>107</v>
+      </c>
+      <c r="B2140" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2140">
+        <v>1</v>
+      </c>
+      <c r="D2140">
+        <v>5775</v>
+      </c>
+      <c r="E2140">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2141">
+        <v>107</v>
+      </c>
+      <c r="B2141" s="10">
+        <v>46027</v>
+      </c>
+      <c r="C2141">
+        <v>1</v>
+      </c>
+      <c r="D2141">
+        <v>295</v>
+      </c>
+      <c r="E2141">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2142">
+        <v>108</v>
+      </c>
+      <c r="B2142" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2142">
+        <v>0</v>
+      </c>
+      <c r="D2142">
+        <v>8590</v>
+      </c>
+      <c r="E2142">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2143">
+        <v>108</v>
+      </c>
+      <c r="B2143" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2143">
+        <v>0</v>
+      </c>
+      <c r="D2143">
+        <v>4935</v>
+      </c>
+      <c r="E2143">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2144">
+        <v>108</v>
+      </c>
+      <c r="B2144" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2144">
+        <v>0</v>
+      </c>
+      <c r="D2144">
+        <v>944</v>
+      </c>
+      <c r="E2144">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2145">
+        <v>108</v>
+      </c>
+      <c r="B2145" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2145">
+        <v>0</v>
+      </c>
+      <c r="D2145">
+        <v>2584</v>
+      </c>
+      <c r="E2145">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2146">
+        <v>108</v>
+      </c>
+      <c r="B2146" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2146">
+        <v>0</v>
+      </c>
+      <c r="D2146">
+        <v>6255</v>
+      </c>
+      <c r="E2146">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2147">
+        <v>108</v>
+      </c>
+      <c r="B2147" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2147">
+        <v>0</v>
+      </c>
+      <c r="D2147">
+        <v>2059</v>
+      </c>
+      <c r="E2147">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2148">
+        <v>108</v>
+      </c>
+      <c r="B2148" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2148">
+        <v>0</v>
+      </c>
+      <c r="D2148">
+        <v>2446</v>
+      </c>
+      <c r="E2148">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2149">
+        <v>108</v>
+      </c>
+      <c r="B2149" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2149">
+        <v>0</v>
+      </c>
+      <c r="D2149">
+        <v>6263</v>
+      </c>
+      <c r="E2149">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2150">
+        <v>108</v>
+      </c>
+      <c r="B2150" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2150">
+        <v>0</v>
+      </c>
+      <c r="D2150">
+        <v>6680</v>
+      </c>
+      <c r="E2150">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2151">
+        <v>108</v>
+      </c>
+      <c r="B2151" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2151">
+        <v>0</v>
+      </c>
+      <c r="D2151">
+        <v>441</v>
+      </c>
+      <c r="E2151">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2152">
+        <v>108</v>
+      </c>
+      <c r="B2152" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2152">
+        <v>1</v>
+      </c>
+      <c r="D2152">
+        <v>634</v>
+      </c>
+      <c r="E2152">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2153">
+        <v>108</v>
+      </c>
+      <c r="B2153" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2153">
+        <v>1</v>
+      </c>
+      <c r="D2153">
+        <v>2062</v>
+      </c>
+      <c r="E2153">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2154">
+        <v>108</v>
+      </c>
+      <c r="B2154" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2154">
+        <v>1</v>
+      </c>
+      <c r="D2154">
+        <v>4215</v>
+      </c>
+      <c r="E2154">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2155">
+        <v>108</v>
+      </c>
+      <c r="B2155" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2155">
+        <v>1</v>
+      </c>
+      <c r="D2155">
+        <v>5211</v>
+      </c>
+      <c r="E2155">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2156">
+        <v>108</v>
+      </c>
+      <c r="B2156" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2156">
+        <v>1</v>
+      </c>
+      <c r="D2156">
+        <v>5083</v>
+      </c>
+      <c r="E2156">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2157">
+        <v>108</v>
+      </c>
+      <c r="B2157" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2157">
+        <v>1</v>
+      </c>
+      <c r="D2157">
+        <v>9633</v>
+      </c>
+      <c r="E2157">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2158">
+        <v>108</v>
+      </c>
+      <c r="B2158" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2158">
+        <v>1</v>
+      </c>
+      <c r="D2158">
+        <v>3020</v>
+      </c>
+      <c r="E2158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2159">
+        <v>108</v>
+      </c>
+      <c r="B2159" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2159">
+        <v>1</v>
+      </c>
+      <c r="D2159">
+        <v>7859</v>
+      </c>
+      <c r="E2159">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2160">
+        <v>108</v>
+      </c>
+      <c r="B2160" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2160">
+        <v>1</v>
+      </c>
+      <c r="D2160">
+        <v>7480</v>
+      </c>
+      <c r="E2160">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2161">
+        <v>108</v>
+      </c>
+      <c r="B2161" s="10">
+        <v>46028</v>
+      </c>
+      <c r="C2161">
+        <v>1</v>
+      </c>
+      <c r="D2161">
+        <v>7794</v>
+      </c>
+      <c r="E2161">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2162">
+        <v>109</v>
+      </c>
+      <c r="B2162" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2162">
+        <v>0</v>
+      </c>
+      <c r="D2162">
+        <v>2212</v>
+      </c>
+      <c r="E2162">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2163">
+        <v>109</v>
+      </c>
+      <c r="B2163" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2163">
+        <v>0</v>
+      </c>
+      <c r="D2163">
+        <v>6050</v>
+      </c>
+      <c r="E2163">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2164">
+        <v>109</v>
+      </c>
+      <c r="B2164" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2164">
+        <v>0</v>
+      </c>
+      <c r="D2164">
+        <v>2117</v>
+      </c>
+      <c r="E2164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2165">
+        <v>109</v>
+      </c>
+      <c r="B2165" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2165">
+        <v>0</v>
+      </c>
+      <c r="D2165">
+        <v>3954</v>
+      </c>
+      <c r="E2165">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2166">
+        <v>109</v>
+      </c>
+      <c r="B2166" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2166">
+        <v>0</v>
+      </c>
+      <c r="D2166">
+        <v>3594</v>
+      </c>
+      <c r="E2166">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2167">
+        <v>109</v>
+      </c>
+      <c r="B2167" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2167">
+        <v>0</v>
+      </c>
+      <c r="D2167">
+        <v>4373</v>
+      </c>
+      <c r="E2167">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2168">
+        <v>109</v>
+      </c>
+      <c r="B2168" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2168">
+        <v>0</v>
+      </c>
+      <c r="D2168">
+        <v>2880</v>
+      </c>
+      <c r="E2168">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2169">
+        <v>109</v>
+      </c>
+      <c r="B2169" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2169">
+        <v>0</v>
+      </c>
+      <c r="D2169">
+        <v>162</v>
+      </c>
+      <c r="E2169">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2170">
+        <v>109</v>
+      </c>
+      <c r="B2170" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2170">
+        <v>0</v>
+      </c>
+      <c r="D2170">
+        <v>6514</v>
+      </c>
+      <c r="E2170">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2171">
+        <v>109</v>
+      </c>
+      <c r="B2171" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2171">
+        <v>0</v>
+      </c>
+      <c r="D2171">
+        <v>4087</v>
+      </c>
+      <c r="E2171">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2172">
+        <v>109</v>
+      </c>
+      <c r="B2172" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2172">
+        <v>1</v>
+      </c>
+      <c r="D2172">
+        <v>4981</v>
+      </c>
+      <c r="E2172">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2173">
+        <v>109</v>
+      </c>
+      <c r="B2173" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2173">
+        <v>1</v>
+      </c>
+      <c r="D2173">
+        <v>5171</v>
+      </c>
+      <c r="E2173">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2174">
+        <v>109</v>
+      </c>
+      <c r="B2174" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2174">
+        <v>1</v>
+      </c>
+      <c r="D2174">
+        <v>5289</v>
+      </c>
+      <c r="E2174">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2175">
+        <v>109</v>
+      </c>
+      <c r="B2175" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2175">
+        <v>1</v>
+      </c>
+      <c r="D2175">
+        <v>1813</v>
+      </c>
+      <c r="E2175">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2176">
+        <v>109</v>
+      </c>
+      <c r="B2176" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2176">
+        <v>1</v>
+      </c>
+      <c r="D2176">
+        <v>9299</v>
+      </c>
+      <c r="E2176">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2177">
+        <v>109</v>
+      </c>
+      <c r="B2177" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2177">
+        <v>1</v>
+      </c>
+      <c r="D2177">
+        <v>4941</v>
+      </c>
+      <c r="E2177">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2178">
+        <v>109</v>
+      </c>
+      <c r="B2178" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2178">
+        <v>1</v>
+      </c>
+      <c r="D2178">
+        <v>315</v>
+      </c>
+      <c r="E2178">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2179">
+        <v>109</v>
+      </c>
+      <c r="B2179" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2179">
+        <v>1</v>
+      </c>
+      <c r="D2179">
+        <v>4570</v>
+      </c>
+      <c r="E2179">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2180">
+        <v>109</v>
+      </c>
+      <c r="B2180" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2180">
+        <v>1</v>
+      </c>
+      <c r="D2180">
+        <v>5665</v>
+      </c>
+      <c r="E2180">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2181">
+        <v>109</v>
+      </c>
+      <c r="B2181" s="10">
+        <v>46029</v>
+      </c>
+      <c r="C2181">
+        <v>1</v>
+      </c>
+      <c r="D2181">
+        <v>9730</v>
+      </c>
+      <c r="E2181">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5910E270-C306-413C-941C-CAB0BDAEB35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8F5002-55DF-4743-8D4D-92C19096E0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2181"/>
+  <dimension ref="A1:T2211"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -38418,6 +38418,486 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2182">
+        <v>110</v>
+      </c>
+      <c r="B2182" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2182">
+        <v>0</v>
+      </c>
+      <c r="D2182">
+        <v>5714</v>
+      </c>
+      <c r="E2182">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2183">
+        <v>110</v>
+      </c>
+      <c r="B2183" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2183">
+        <v>0</v>
+      </c>
+      <c r="D2183">
+        <v>5336</v>
+      </c>
+      <c r="E2183">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2184">
+        <v>110</v>
+      </c>
+      <c r="B2184" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2184">
+        <v>0</v>
+      </c>
+      <c r="D2184">
+        <v>8238</v>
+      </c>
+      <c r="E2184">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2185">
+        <v>110</v>
+      </c>
+      <c r="B2185" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2185">
+        <v>0</v>
+      </c>
+      <c r="D2185">
+        <v>9191</v>
+      </c>
+      <c r="E2185">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2186">
+        <v>110</v>
+      </c>
+      <c r="B2186" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2186">
+        <v>0</v>
+      </c>
+      <c r="D2186">
+        <v>4249</v>
+      </c>
+      <c r="E2186">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2187">
+        <v>110</v>
+      </c>
+      <c r="B2187" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2187">
+        <v>0</v>
+      </c>
+      <c r="D2187">
+        <v>9761</v>
+      </c>
+      <c r="E2187">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2188">
+        <v>110</v>
+      </c>
+      <c r="B2188" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2188">
+        <v>0</v>
+      </c>
+      <c r="D2188">
+        <v>3937</v>
+      </c>
+      <c r="E2188">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2189">
+        <v>110</v>
+      </c>
+      <c r="B2189" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2189">
+        <v>0</v>
+      </c>
+      <c r="D2189">
+        <v>5711</v>
+      </c>
+      <c r="E2189">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2190">
+        <v>110</v>
+      </c>
+      <c r="B2190" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2190">
+        <v>0</v>
+      </c>
+      <c r="D2190">
+        <v>9283</v>
+      </c>
+      <c r="E2190">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2191">
+        <v>110</v>
+      </c>
+      <c r="B2191" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2191">
+        <v>0</v>
+      </c>
+      <c r="D2191">
+        <v>8792</v>
+      </c>
+      <c r="E2191">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2192">
+        <v>110</v>
+      </c>
+      <c r="B2192" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2192">
+        <v>1</v>
+      </c>
+      <c r="D2192">
+        <v>2558</v>
+      </c>
+      <c r="E2192">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2193">
+        <v>110</v>
+      </c>
+      <c r="B2193" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2193">
+        <v>1</v>
+      </c>
+      <c r="D2193">
+        <v>6989</v>
+      </c>
+      <c r="E2193">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2194">
+        <v>110</v>
+      </c>
+      <c r="B2194" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2194">
+        <v>1</v>
+      </c>
+      <c r="D2194">
+        <v>5078</v>
+      </c>
+      <c r="E2194">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2195">
+        <v>110</v>
+      </c>
+      <c r="B2195" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2195">
+        <v>1</v>
+      </c>
+      <c r="D2195">
+        <v>3184</v>
+      </c>
+      <c r="E2195">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2196">
+        <v>110</v>
+      </c>
+      <c r="B2196" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2196">
+        <v>1</v>
+      </c>
+      <c r="D2196">
+        <v>3454</v>
+      </c>
+      <c r="E2196">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2197">
+        <v>110</v>
+      </c>
+      <c r="B2197" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2197">
+        <v>1</v>
+      </c>
+      <c r="D2197">
+        <v>1188</v>
+      </c>
+      <c r="E2197">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2198">
+        <v>110</v>
+      </c>
+      <c r="B2198" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2198">
+        <v>1</v>
+      </c>
+      <c r="D2198">
+        <v>2243</v>
+      </c>
+      <c r="E2198">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2199">
+        <v>110</v>
+      </c>
+      <c r="B2199" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2199">
+        <v>1</v>
+      </c>
+      <c r="D2199">
+        <v>4365</v>
+      </c>
+      <c r="E2199">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2200">
+        <v>110</v>
+      </c>
+      <c r="B2200" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2200">
+        <v>1</v>
+      </c>
+      <c r="D2200">
+        <v>6547</v>
+      </c>
+      <c r="E2200">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2201">
+        <v>110</v>
+      </c>
+      <c r="B2201" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C2201">
+        <v>1</v>
+      </c>
+      <c r="D2201">
+        <v>6376</v>
+      </c>
+      <c r="E2201">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2202" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2202">
+        <v>0</v>
+      </c>
+      <c r="D2202">
+        <v>2720</v>
+      </c>
+      <c r="E2202">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2203" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2203">
+        <v>0</v>
+      </c>
+      <c r="D2203">
+        <v>6449</v>
+      </c>
+      <c r="E2203">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2204" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2204">
+        <v>0</v>
+      </c>
+      <c r="D2204">
+        <v>4735</v>
+      </c>
+      <c r="E2204">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2205" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2205">
+        <v>0</v>
+      </c>
+      <c r="D2205">
+        <v>343</v>
+      </c>
+      <c r="E2205">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2206" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2206">
+        <v>0</v>
+      </c>
+      <c r="D2206">
+        <v>8468</v>
+      </c>
+      <c r="E2206">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2207" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2207">
+        <v>0</v>
+      </c>
+      <c r="D2207">
+        <v>3501</v>
+      </c>
+      <c r="E2207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B2208" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2208">
+        <v>0</v>
+      </c>
+      <c r="D2208">
+        <v>48</v>
+      </c>
+      <c r="E2208">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2209" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2209" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2209">
+        <v>0</v>
+      </c>
+      <c r="D2209">
+        <v>2313</v>
+      </c>
+      <c r="E2209">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2210" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2210" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2210">
+        <v>0</v>
+      </c>
+      <c r="D2210">
+        <v>62</v>
+      </c>
+      <c r="E2210">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2211" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2211" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2211">
+        <v>0</v>
+      </c>
+      <c r="D2211">
+        <v>7512</v>
+      </c>
+      <c r="E2211">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8F5002-55DF-4743-8D4D-92C19096E0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA6F64F-81E5-4FDE-B8C7-8D71396140C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2211"/>
+  <dimension ref="A1:T2231"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -38759,6 +38759,9 @@
       </c>
     </row>
     <row r="2202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2202">
+        <v>111</v>
+      </c>
       <c r="B2202" s="10">
         <v>46031</v>
       </c>
@@ -38773,6 +38776,9 @@
       </c>
     </row>
     <row r="2203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2203">
+        <v>111</v>
+      </c>
       <c r="B2203" s="10">
         <v>46031</v>
       </c>
@@ -38787,6 +38793,9 @@
       </c>
     </row>
     <row r="2204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2204">
+        <v>111</v>
+      </c>
       <c r="B2204" s="10">
         <v>46031</v>
       </c>
@@ -38801,6 +38810,9 @@
       </c>
     </row>
     <row r="2205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2205">
+        <v>111</v>
+      </c>
       <c r="B2205" s="10">
         <v>46031</v>
       </c>
@@ -38815,6 +38827,9 @@
       </c>
     </row>
     <row r="2206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2206">
+        <v>111</v>
+      </c>
       <c r="B2206" s="10">
         <v>46031</v>
       </c>
@@ -38829,6 +38844,9 @@
       </c>
     </row>
     <row r="2207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2207">
+        <v>111</v>
+      </c>
       <c r="B2207" s="10">
         <v>46031</v>
       </c>
@@ -38843,6 +38861,9 @@
       </c>
     </row>
     <row r="2208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2208">
+        <v>111</v>
+      </c>
       <c r="B2208" s="10">
         <v>46031</v>
       </c>
@@ -38856,7 +38877,10 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2209" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2209">
+        <v>111</v>
+      </c>
       <c r="B2209" s="10">
         <v>46031</v>
       </c>
@@ -38870,7 +38894,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2210" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2210">
+        <v>111</v>
+      </c>
       <c r="B2210" s="10">
         <v>46031</v>
       </c>
@@ -38884,7 +38911,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2211" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="2211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2211">
+        <v>111</v>
+      </c>
       <c r="B2211" s="10">
         <v>46031</v>
       </c>
@@ -38896,6 +38926,346 @@
       </c>
       <c r="E2211">
         <v>3</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2212">
+        <v>111</v>
+      </c>
+      <c r="B2212" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2212">
+        <v>1</v>
+      </c>
+      <c r="D2212">
+        <v>5505</v>
+      </c>
+      <c r="E2212">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2213">
+        <v>111</v>
+      </c>
+      <c r="B2213" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2213">
+        <v>1</v>
+      </c>
+      <c r="D2213">
+        <v>4670</v>
+      </c>
+      <c r="E2213">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2214">
+        <v>111</v>
+      </c>
+      <c r="B2214" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2214">
+        <v>1</v>
+      </c>
+      <c r="D2214">
+        <v>5565</v>
+      </c>
+      <c r="E2214">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2215">
+        <v>111</v>
+      </c>
+      <c r="B2215" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2215">
+        <v>1</v>
+      </c>
+      <c r="D2215">
+        <v>4123</v>
+      </c>
+      <c r="E2215">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2216">
+        <v>111</v>
+      </c>
+      <c r="B2216" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2216">
+        <v>1</v>
+      </c>
+      <c r="D2216">
+        <v>990</v>
+      </c>
+      <c r="E2216">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2217">
+        <v>111</v>
+      </c>
+      <c r="B2217" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2217">
+        <v>1</v>
+      </c>
+      <c r="D2217">
+        <v>4627</v>
+      </c>
+      <c r="E2217">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2218">
+        <v>111</v>
+      </c>
+      <c r="B2218" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2218">
+        <v>1</v>
+      </c>
+      <c r="D2218">
+        <v>9754</v>
+      </c>
+      <c r="E2218">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2219">
+        <v>111</v>
+      </c>
+      <c r="B2219" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2219">
+        <v>1</v>
+      </c>
+      <c r="D2219">
+        <v>8266</v>
+      </c>
+      <c r="E2219">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2220">
+        <v>111</v>
+      </c>
+      <c r="B2220" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2220">
+        <v>1</v>
+      </c>
+      <c r="D2220">
+        <v>4185</v>
+      </c>
+      <c r="E2220">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2221">
+        <v>111</v>
+      </c>
+      <c r="B2221" s="10">
+        <v>46031</v>
+      </c>
+      <c r="C2221">
+        <v>1</v>
+      </c>
+      <c r="D2221">
+        <v>6279</v>
+      </c>
+      <c r="E2221">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2222">
+        <v>112</v>
+      </c>
+      <c r="B2222" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2222">
+        <v>0</v>
+      </c>
+      <c r="D2222">
+        <v>8117</v>
+      </c>
+      <c r="E2222">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2223">
+        <v>112</v>
+      </c>
+      <c r="B2223" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2223">
+        <v>0</v>
+      </c>
+      <c r="D2223">
+        <v>5019</v>
+      </c>
+      <c r="E2223">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2224">
+        <v>112</v>
+      </c>
+      <c r="B2224" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2224">
+        <v>0</v>
+      </c>
+      <c r="D2224">
+        <v>3185</v>
+      </c>
+      <c r="E2224">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2225">
+        <v>112</v>
+      </c>
+      <c r="B2225" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2225">
+        <v>0</v>
+      </c>
+      <c r="D2225">
+        <v>9214</v>
+      </c>
+      <c r="E2225">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2226">
+        <v>112</v>
+      </c>
+      <c r="B2226" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2226">
+        <v>0</v>
+      </c>
+      <c r="D2226">
+        <v>4502</v>
+      </c>
+      <c r="E2226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2227">
+        <v>112</v>
+      </c>
+      <c r="B2227" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2227">
+        <v>0</v>
+      </c>
+      <c r="D2227">
+        <v>2464</v>
+      </c>
+      <c r="E2227">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2228">
+        <v>112</v>
+      </c>
+      <c r="B2228" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2228">
+        <v>0</v>
+      </c>
+      <c r="D2228">
+        <v>9624</v>
+      </c>
+      <c r="E2228">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2229">
+        <v>112</v>
+      </c>
+      <c r="B2229" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2229">
+        <v>0</v>
+      </c>
+      <c r="D2229">
+        <v>8681</v>
+      </c>
+      <c r="E2229">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2230">
+        <v>112</v>
+      </c>
+      <c r="B2230" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2230">
+        <v>0</v>
+      </c>
+      <c r="D2230">
+        <v>6067</v>
+      </c>
+      <c r="E2230">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2231">
+        <v>112</v>
+      </c>
+      <c r="B2231" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2231">
+        <v>0</v>
+      </c>
+      <c r="D2231">
+        <v>7778</v>
+      </c>
+      <c r="E2231">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA6F64F-81E5-4FDE-B8C7-8D71396140C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8F07BA-ABB1-40F6-8185-73FC5A78C110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2231"/>
+  <dimension ref="A1:T2241"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -39268,6 +39268,176 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2232" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2232">
+        <v>112</v>
+      </c>
+      <c r="B2232" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2232">
+        <v>1</v>
+      </c>
+      <c r="D2232">
+        <v>7551</v>
+      </c>
+      <c r="E2232">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2233">
+        <v>112</v>
+      </c>
+      <c r="B2233" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2233">
+        <v>1</v>
+      </c>
+      <c r="D2233">
+        <v>4285</v>
+      </c>
+      <c r="E2233">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2234">
+        <v>112</v>
+      </c>
+      <c r="B2234" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2234">
+        <v>1</v>
+      </c>
+      <c r="D2234">
+        <v>2375</v>
+      </c>
+      <c r="E2234">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2235">
+        <v>112</v>
+      </c>
+      <c r="B2235" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2235">
+        <v>1</v>
+      </c>
+      <c r="D2235">
+        <v>1154</v>
+      </c>
+      <c r="E2235">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2236">
+        <v>112</v>
+      </c>
+      <c r="B2236" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2236">
+        <v>1</v>
+      </c>
+      <c r="D2236">
+        <v>3701</v>
+      </c>
+      <c r="E2236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2237">
+        <v>112</v>
+      </c>
+      <c r="B2237" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2237">
+        <v>1</v>
+      </c>
+      <c r="D2237">
+        <v>5620</v>
+      </c>
+      <c r="E2237">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2238">
+        <v>112</v>
+      </c>
+      <c r="B2238" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2238">
+        <v>1</v>
+      </c>
+      <c r="D2238">
+        <v>2035</v>
+      </c>
+      <c r="E2238">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2239">
+        <v>112</v>
+      </c>
+      <c r="B2239" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2239">
+        <v>1</v>
+      </c>
+      <c r="D2239">
+        <v>3947</v>
+      </c>
+      <c r="E2239">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2240">
+        <v>112</v>
+      </c>
+      <c r="B2240" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2240">
+        <v>1</v>
+      </c>
+      <c r="D2240">
+        <v>5101</v>
+      </c>
+      <c r="E2240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2241">
+        <v>112</v>
+      </c>
+      <c r="B2241" s="10">
+        <v>46032</v>
+      </c>
+      <c r="C2241">
+        <v>1</v>
+      </c>
+      <c r="D2241">
+        <v>3236</v>
+      </c>
+      <c r="E2241">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8F07BA-ABB1-40F6-8185-73FC5A78C110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F30D9F-FC81-4BF1-810C-2975851856AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2241"/>
+  <dimension ref="A1:T2281"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -39438,6 +39438,686 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2242" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2242">
+        <v>113</v>
+      </c>
+      <c r="B2242" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2242">
+        <v>0</v>
+      </c>
+      <c r="D2242">
+        <v>4001</v>
+      </c>
+      <c r="E2242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2243">
+        <v>113</v>
+      </c>
+      <c r="B2243" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2243">
+        <v>0</v>
+      </c>
+      <c r="D2243">
+        <v>2380</v>
+      </c>
+      <c r="E2243">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2244">
+        <v>113</v>
+      </c>
+      <c r="B2244" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2244">
+        <v>0</v>
+      </c>
+      <c r="D2244">
+        <v>9206</v>
+      </c>
+      <c r="E2244">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2245">
+        <v>113</v>
+      </c>
+      <c r="B2245" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2245">
+        <v>0</v>
+      </c>
+      <c r="D2245">
+        <v>452</v>
+      </c>
+      <c r="E2245">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2246">
+        <v>113</v>
+      </c>
+      <c r="B2246" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2246">
+        <v>0</v>
+      </c>
+      <c r="D2246">
+        <v>2836</v>
+      </c>
+      <c r="E2246">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2247">
+        <v>113</v>
+      </c>
+      <c r="B2247" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2247">
+        <v>0</v>
+      </c>
+      <c r="D2247">
+        <v>252</v>
+      </c>
+      <c r="E2247">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2248">
+        <v>113</v>
+      </c>
+      <c r="B2248" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2248">
+        <v>0</v>
+      </c>
+      <c r="D2248">
+        <v>1006</v>
+      </c>
+      <c r="E2248">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2249">
+        <v>113</v>
+      </c>
+      <c r="B2249" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2249">
+        <v>0</v>
+      </c>
+      <c r="D2249">
+        <v>4915</v>
+      </c>
+      <c r="E2249">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2250">
+        <v>113</v>
+      </c>
+      <c r="B2250" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2250">
+        <v>0</v>
+      </c>
+      <c r="D2250">
+        <v>5471</v>
+      </c>
+      <c r="E2250">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2251">
+        <v>113</v>
+      </c>
+      <c r="B2251" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2251">
+        <v>0</v>
+      </c>
+      <c r="D2251">
+        <v>7246</v>
+      </c>
+      <c r="E2251">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2252">
+        <v>113</v>
+      </c>
+      <c r="B2252" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2252">
+        <v>1</v>
+      </c>
+      <c r="D2252">
+        <v>9385</v>
+      </c>
+      <c r="E2252">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2253">
+        <v>113</v>
+      </c>
+      <c r="B2253" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2253">
+        <v>1</v>
+      </c>
+      <c r="D2253">
+        <v>5385</v>
+      </c>
+      <c r="E2253">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2254">
+        <v>113</v>
+      </c>
+      <c r="B2254" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2254">
+        <v>1</v>
+      </c>
+      <c r="D2254">
+        <v>6732</v>
+      </c>
+      <c r="E2254">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2255">
+        <v>113</v>
+      </c>
+      <c r="B2255" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2255">
+        <v>1</v>
+      </c>
+      <c r="D2255">
+        <v>1909</v>
+      </c>
+      <c r="E2255">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2256">
+        <v>113</v>
+      </c>
+      <c r="B2256" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2256">
+        <v>1</v>
+      </c>
+      <c r="D2256">
+        <v>696</v>
+      </c>
+      <c r="E2256">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2257">
+        <v>113</v>
+      </c>
+      <c r="B2257" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2257">
+        <v>1</v>
+      </c>
+      <c r="D2257">
+        <v>9995</v>
+      </c>
+      <c r="E2257">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2258">
+        <v>113</v>
+      </c>
+      <c r="B2258" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2258">
+        <v>1</v>
+      </c>
+      <c r="D2258">
+        <v>8303</v>
+      </c>
+      <c r="E2258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2259">
+        <v>113</v>
+      </c>
+      <c r="B2259" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2259">
+        <v>1</v>
+      </c>
+      <c r="D2259">
+        <v>3991</v>
+      </c>
+      <c r="E2259">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2260">
+        <v>113</v>
+      </c>
+      <c r="B2260" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2260">
+        <v>1</v>
+      </c>
+      <c r="D2260">
+        <v>7189</v>
+      </c>
+      <c r="E2260">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2261">
+        <v>113</v>
+      </c>
+      <c r="B2261" s="10">
+        <v>46034</v>
+      </c>
+      <c r="C2261">
+        <v>1</v>
+      </c>
+      <c r="D2261">
+        <v>4090</v>
+      </c>
+      <c r="E2261">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2262">
+        <v>114</v>
+      </c>
+      <c r="B2262" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2262">
+        <v>0</v>
+      </c>
+      <c r="D2262">
+        <v>3777</v>
+      </c>
+      <c r="E2262">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2263">
+        <v>114</v>
+      </c>
+      <c r="B2263" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2263">
+        <v>0</v>
+      </c>
+      <c r="D2263">
+        <v>550</v>
+      </c>
+      <c r="E2263">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2264">
+        <v>114</v>
+      </c>
+      <c r="B2264" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2264">
+        <v>0</v>
+      </c>
+      <c r="D2264">
+        <v>8260</v>
+      </c>
+      <c r="E2264">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2265">
+        <v>114</v>
+      </c>
+      <c r="B2265" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2265">
+        <v>0</v>
+      </c>
+      <c r="D2265">
+        <v>9425</v>
+      </c>
+      <c r="E2265">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2266">
+        <v>114</v>
+      </c>
+      <c r="B2266" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2266">
+        <v>0</v>
+      </c>
+      <c r="D2266">
+        <v>7948</v>
+      </c>
+      <c r="E2266">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2267">
+        <v>114</v>
+      </c>
+      <c r="B2267" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2267">
+        <v>0</v>
+      </c>
+      <c r="D2267">
+        <v>2145</v>
+      </c>
+      <c r="E2267">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2268">
+        <v>114</v>
+      </c>
+      <c r="B2268" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2268">
+        <v>0</v>
+      </c>
+      <c r="D2268">
+        <v>3325</v>
+      </c>
+      <c r="E2268">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2269">
+        <v>114</v>
+      </c>
+      <c r="B2269" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2269">
+        <v>0</v>
+      </c>
+      <c r="D2269">
+        <v>4216</v>
+      </c>
+      <c r="E2269">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2270">
+        <v>114</v>
+      </c>
+      <c r="B2270" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2270">
+        <v>0</v>
+      </c>
+      <c r="D2270">
+        <v>1609</v>
+      </c>
+      <c r="E2270">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2271">
+        <v>114</v>
+      </c>
+      <c r="B2271" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2271">
+        <v>0</v>
+      </c>
+      <c r="D2271">
+        <v>2856</v>
+      </c>
+      <c r="E2271">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2272">
+        <v>114</v>
+      </c>
+      <c r="B2272" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2272">
+        <v>1</v>
+      </c>
+      <c r="D2272">
+        <v>3174</v>
+      </c>
+      <c r="E2272">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2273">
+        <v>114</v>
+      </c>
+      <c r="B2273" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2273">
+        <v>1</v>
+      </c>
+      <c r="D2273">
+        <v>6979</v>
+      </c>
+      <c r="E2273">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2274">
+        <v>114</v>
+      </c>
+      <c r="B2274" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2274">
+        <v>1</v>
+      </c>
+      <c r="D2274">
+        <v>7735</v>
+      </c>
+      <c r="E2274">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2275">
+        <v>114</v>
+      </c>
+      <c r="B2275" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2275">
+        <v>1</v>
+      </c>
+      <c r="D2275">
+        <v>4865</v>
+      </c>
+      <c r="E2275">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2276">
+        <v>114</v>
+      </c>
+      <c r="B2276" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2276">
+        <v>1</v>
+      </c>
+      <c r="D2276">
+        <v>4056</v>
+      </c>
+      <c r="E2276">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2277">
+        <v>114</v>
+      </c>
+      <c r="B2277" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2277">
+        <v>1</v>
+      </c>
+      <c r="D2277">
+        <v>5002</v>
+      </c>
+      <c r="E2277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2278">
+        <v>114</v>
+      </c>
+      <c r="B2278" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2278">
+        <v>1</v>
+      </c>
+      <c r="D2278">
+        <v>5910</v>
+      </c>
+      <c r="E2278">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2279">
+        <v>114</v>
+      </c>
+      <c r="B2279" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2279">
+        <v>1</v>
+      </c>
+      <c r="D2279">
+        <v>1668</v>
+      </c>
+      <c r="E2279">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2280">
+        <v>114</v>
+      </c>
+      <c r="B2280" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2280">
+        <v>1</v>
+      </c>
+      <c r="D2280">
+        <v>2870</v>
+      </c>
+      <c r="E2280">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2281">
+        <v>114</v>
+      </c>
+      <c r="B2281" s="10">
+        <v>46035</v>
+      </c>
+      <c r="C2281">
+        <v>1</v>
+      </c>
+      <c r="D2281">
+        <v>103</v>
+      </c>
+      <c r="E2281">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F30D9F-FC81-4BF1-810C-2975851856AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1ACD559-6130-4A2B-AB80-C065765A727E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2281"/>
+  <dimension ref="A1:T2321"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -40118,6 +40118,686 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2282" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2282">
+        <v>115</v>
+      </c>
+      <c r="B2282" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2282">
+        <v>0</v>
+      </c>
+      <c r="D2282">
+        <v>1044</v>
+      </c>
+      <c r="E2282">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2283">
+        <v>115</v>
+      </c>
+      <c r="B2283" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2283">
+        <v>0</v>
+      </c>
+      <c r="D2283">
+        <v>6324</v>
+      </c>
+      <c r="E2283">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2284">
+        <v>115</v>
+      </c>
+      <c r="B2284" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2284">
+        <v>0</v>
+      </c>
+      <c r="D2284">
+        <v>3485</v>
+      </c>
+      <c r="E2284">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2285">
+        <v>115</v>
+      </c>
+      <c r="B2285" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2285">
+        <v>0</v>
+      </c>
+      <c r="D2285">
+        <v>5525</v>
+      </c>
+      <c r="E2285">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2286">
+        <v>115</v>
+      </c>
+      <c r="B2286" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2286">
+        <v>0</v>
+      </c>
+      <c r="D2286">
+        <v>7482</v>
+      </c>
+      <c r="E2286">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2287">
+        <v>115</v>
+      </c>
+      <c r="B2287" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2287">
+        <v>0</v>
+      </c>
+      <c r="D2287">
+        <v>6426</v>
+      </c>
+      <c r="E2287">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2288">
+        <v>115</v>
+      </c>
+      <c r="B2288" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2288">
+        <v>0</v>
+      </c>
+      <c r="D2288">
+        <v>66</v>
+      </c>
+      <c r="E2288">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2289">
+        <v>115</v>
+      </c>
+      <c r="B2289" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2289">
+        <v>0</v>
+      </c>
+      <c r="D2289">
+        <v>29</v>
+      </c>
+      <c r="E2289">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2290">
+        <v>115</v>
+      </c>
+      <c r="B2290" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2290">
+        <v>0</v>
+      </c>
+      <c r="D2290">
+        <v>163</v>
+      </c>
+      <c r="E2290">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2291">
+        <v>115</v>
+      </c>
+      <c r="B2291" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2291">
+        <v>0</v>
+      </c>
+      <c r="D2291">
+        <v>4086</v>
+      </c>
+      <c r="E2291">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2292">
+        <v>115</v>
+      </c>
+      <c r="B2292" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2292">
+        <v>1</v>
+      </c>
+      <c r="D2292">
+        <v>9935</v>
+      </c>
+      <c r="E2292">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2293">
+        <v>115</v>
+      </c>
+      <c r="B2293" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2293">
+        <v>1</v>
+      </c>
+      <c r="D2293">
+        <v>5097</v>
+      </c>
+      <c r="E2293">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2294">
+        <v>115</v>
+      </c>
+      <c r="B2294" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2294">
+        <v>1</v>
+      </c>
+      <c r="D2294">
+        <v>703</v>
+      </c>
+      <c r="E2294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2295">
+        <v>115</v>
+      </c>
+      <c r="B2295" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2295">
+        <v>1</v>
+      </c>
+      <c r="D2295">
+        <v>5297</v>
+      </c>
+      <c r="E2295">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2296">
+        <v>115</v>
+      </c>
+      <c r="B2296" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2296">
+        <v>1</v>
+      </c>
+      <c r="D2296">
+        <v>2774</v>
+      </c>
+      <c r="E2296">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2297">
+        <v>115</v>
+      </c>
+      <c r="B2297" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2297">
+        <v>1</v>
+      </c>
+      <c r="D2297">
+        <v>2101</v>
+      </c>
+      <c r="E2297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2298">
+        <v>115</v>
+      </c>
+      <c r="B2298" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2298">
+        <v>1</v>
+      </c>
+      <c r="D2298">
+        <v>5792</v>
+      </c>
+      <c r="E2298">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2299">
+        <v>115</v>
+      </c>
+      <c r="B2299" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2299">
+        <v>1</v>
+      </c>
+      <c r="D2299">
+        <v>836</v>
+      </c>
+      <c r="E2299">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2300">
+        <v>115</v>
+      </c>
+      <c r="B2300" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2300">
+        <v>1</v>
+      </c>
+      <c r="D2300">
+        <v>1374</v>
+      </c>
+      <c r="E2300">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2301">
+        <v>115</v>
+      </c>
+      <c r="B2301" s="10">
+        <v>46036</v>
+      </c>
+      <c r="C2301">
+        <v>1</v>
+      </c>
+      <c r="D2301">
+        <v>7336</v>
+      </c>
+      <c r="E2301">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2302">
+        <v>116</v>
+      </c>
+      <c r="B2302" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2302">
+        <v>0</v>
+      </c>
+      <c r="D2302">
+        <v>2102</v>
+      </c>
+      <c r="E2302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2303">
+        <v>116</v>
+      </c>
+      <c r="B2303" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2303">
+        <v>0</v>
+      </c>
+      <c r="D2303">
+        <v>6711</v>
+      </c>
+      <c r="E2303">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2304">
+        <v>116</v>
+      </c>
+      <c r="B2304" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2304">
+        <v>0</v>
+      </c>
+      <c r="D2304">
+        <v>2677</v>
+      </c>
+      <c r="E2304">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2305">
+        <v>116</v>
+      </c>
+      <c r="B2305" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2305">
+        <v>0</v>
+      </c>
+      <c r="D2305">
+        <v>4667</v>
+      </c>
+      <c r="E2305">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2306">
+        <v>116</v>
+      </c>
+      <c r="B2306" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2306">
+        <v>0</v>
+      </c>
+      <c r="D2306">
+        <v>579</v>
+      </c>
+      <c r="E2306">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2307">
+        <v>116</v>
+      </c>
+      <c r="B2307" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2307">
+        <v>0</v>
+      </c>
+      <c r="D2307">
+        <v>4299</v>
+      </c>
+      <c r="E2307">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2308">
+        <v>116</v>
+      </c>
+      <c r="B2308" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2308">
+        <v>0</v>
+      </c>
+      <c r="D2308">
+        <v>9288</v>
+      </c>
+      <c r="E2308">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2309">
+        <v>116</v>
+      </c>
+      <c r="B2309" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2309">
+        <v>0</v>
+      </c>
+      <c r="D2309">
+        <v>1803</v>
+      </c>
+      <c r="E2309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2310">
+        <v>116</v>
+      </c>
+      <c r="B2310" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2310">
+        <v>0</v>
+      </c>
+      <c r="D2310">
+        <v>6571</v>
+      </c>
+      <c r="E2310">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2311">
+        <v>116</v>
+      </c>
+      <c r="B2311" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2311">
+        <v>0</v>
+      </c>
+      <c r="D2311">
+        <v>4897</v>
+      </c>
+      <c r="E2311">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2312">
+        <v>116</v>
+      </c>
+      <c r="B2312" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2312">
+        <v>1</v>
+      </c>
+      <c r="D2312">
+        <v>4706</v>
+      </c>
+      <c r="E2312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2313">
+        <v>116</v>
+      </c>
+      <c r="B2313" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2313">
+        <v>1</v>
+      </c>
+      <c r="D2313">
+        <v>9925</v>
+      </c>
+      <c r="E2313">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2314">
+        <v>116</v>
+      </c>
+      <c r="B2314" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2314">
+        <v>1</v>
+      </c>
+      <c r="D2314">
+        <v>1678</v>
+      </c>
+      <c r="E2314">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2315">
+        <v>116</v>
+      </c>
+      <c r="B2315" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2315">
+        <v>1</v>
+      </c>
+      <c r="D2315">
+        <v>3074</v>
+      </c>
+      <c r="E2315">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2316">
+        <v>116</v>
+      </c>
+      <c r="B2316" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2316">
+        <v>1</v>
+      </c>
+      <c r="D2316">
+        <v>7942</v>
+      </c>
+      <c r="E2316">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2317">
+        <v>116</v>
+      </c>
+      <c r="B2317" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2317">
+        <v>1</v>
+      </c>
+      <c r="D2317">
+        <v>1011</v>
+      </c>
+      <c r="E2317">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2318">
+        <v>116</v>
+      </c>
+      <c r="B2318" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2318">
+        <v>1</v>
+      </c>
+      <c r="D2318">
+        <v>6413</v>
+      </c>
+      <c r="E2318">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2319">
+        <v>116</v>
+      </c>
+      <c r="B2319" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2319">
+        <v>1</v>
+      </c>
+      <c r="D2319">
+        <v>2751</v>
+      </c>
+      <c r="E2319">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2320">
+        <v>116</v>
+      </c>
+      <c r="B2320" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2320">
+        <v>1</v>
+      </c>
+      <c r="D2320">
+        <v>1764</v>
+      </c>
+      <c r="E2320">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2321">
+        <v>116</v>
+      </c>
+      <c r="B2321" s="10">
+        <v>46037</v>
+      </c>
+      <c r="C2321">
+        <v>1</v>
+      </c>
+      <c r="D2321">
+        <v>4008</v>
+      </c>
+      <c r="E2321">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1ACD559-6130-4A2B-AB80-C065765A727E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505A374F-8596-4BA7-B272-808215019B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2321"/>
+  <dimension ref="A1:T2351"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -40798,6 +40798,516 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2322" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2322">
+        <v>117</v>
+      </c>
+      <c r="B2322" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2322">
+        <v>0</v>
+      </c>
+      <c r="D2322">
+        <v>9471</v>
+      </c>
+      <c r="E2322">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2323">
+        <v>117</v>
+      </c>
+      <c r="B2323" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2323">
+        <v>0</v>
+      </c>
+      <c r="D2323">
+        <v>5902</v>
+      </c>
+      <c r="E2323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2324">
+        <v>117</v>
+      </c>
+      <c r="B2324" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2324">
+        <v>0</v>
+      </c>
+      <c r="D2324">
+        <v>5958</v>
+      </c>
+      <c r="E2324">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2325">
+        <v>117</v>
+      </c>
+      <c r="B2325" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2325">
+        <v>0</v>
+      </c>
+      <c r="D2325">
+        <v>5794</v>
+      </c>
+      <c r="E2325">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2326">
+        <v>117</v>
+      </c>
+      <c r="B2326" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2326">
+        <v>0</v>
+      </c>
+      <c r="D2326">
+        <v>8434</v>
+      </c>
+      <c r="E2326">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2327">
+        <v>117</v>
+      </c>
+      <c r="B2327" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2327">
+        <v>0</v>
+      </c>
+      <c r="D2327">
+        <v>9170</v>
+      </c>
+      <c r="E2327">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2328">
+        <v>117</v>
+      </c>
+      <c r="B2328" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2328">
+        <v>0</v>
+      </c>
+      <c r="D2328">
+        <v>8408</v>
+      </c>
+      <c r="E2328">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2329">
+        <v>117</v>
+      </c>
+      <c r="B2329" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2329">
+        <v>0</v>
+      </c>
+      <c r="D2329">
+        <v>2593</v>
+      </c>
+      <c r="E2329">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2330">
+        <v>117</v>
+      </c>
+      <c r="B2330" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2330">
+        <v>0</v>
+      </c>
+      <c r="D2330">
+        <v>3100</v>
+      </c>
+      <c r="E2330">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2331">
+        <v>117</v>
+      </c>
+      <c r="B2331" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2331">
+        <v>0</v>
+      </c>
+      <c r="D2331">
+        <v>5856</v>
+      </c>
+      <c r="E2331">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2332">
+        <v>117</v>
+      </c>
+      <c r="B2332" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2332">
+        <v>1</v>
+      </c>
+      <c r="D2332">
+        <v>2371</v>
+      </c>
+      <c r="E2332">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2333">
+        <v>117</v>
+      </c>
+      <c r="B2333" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2333">
+        <v>1</v>
+      </c>
+      <c r="D2333">
+        <v>4266</v>
+      </c>
+      <c r="E2333">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2334">
+        <v>117</v>
+      </c>
+      <c r="B2334" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2334">
+        <v>1</v>
+      </c>
+      <c r="D2334">
+        <v>9275</v>
+      </c>
+      <c r="E2334">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2335">
+        <v>117</v>
+      </c>
+      <c r="B2335" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2335">
+        <v>1</v>
+      </c>
+      <c r="D2335">
+        <v>6352</v>
+      </c>
+      <c r="E2335">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2336">
+        <v>117</v>
+      </c>
+      <c r="B2336" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2336">
+        <v>1</v>
+      </c>
+      <c r="D2336">
+        <v>4087</v>
+      </c>
+      <c r="E2336">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2337">
+        <v>117</v>
+      </c>
+      <c r="B2337" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2337">
+        <v>1</v>
+      </c>
+      <c r="D2337">
+        <v>6793</v>
+      </c>
+      <c r="E2337">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2338">
+        <v>117</v>
+      </c>
+      <c r="B2338" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2338">
+        <v>1</v>
+      </c>
+      <c r="D2338">
+        <v>8109</v>
+      </c>
+      <c r="E2338">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2339">
+        <v>117</v>
+      </c>
+      <c r="B2339" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2339">
+        <v>1</v>
+      </c>
+      <c r="D2339">
+        <v>101</v>
+      </c>
+      <c r="E2339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2340">
+        <v>117</v>
+      </c>
+      <c r="B2340" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2340">
+        <v>1</v>
+      </c>
+      <c r="D2340">
+        <v>6727</v>
+      </c>
+      <c r="E2340">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2341">
+        <v>117</v>
+      </c>
+      <c r="B2341" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2341">
+        <v>1</v>
+      </c>
+      <c r="D2341">
+        <v>9688</v>
+      </c>
+      <c r="E2341">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2342">
+        <v>118</v>
+      </c>
+      <c r="B2342" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2342">
+        <v>0</v>
+      </c>
+      <c r="D2342">
+        <v>4855</v>
+      </c>
+      <c r="E2342">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2343">
+        <v>118</v>
+      </c>
+      <c r="B2343" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2343">
+        <v>0</v>
+      </c>
+      <c r="D2343">
+        <v>7141</v>
+      </c>
+      <c r="E2343">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2344">
+        <v>118</v>
+      </c>
+      <c r="B2344" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2344">
+        <v>0</v>
+      </c>
+      <c r="D2344">
+        <v>4432</v>
+      </c>
+      <c r="E2344">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2345">
+        <v>118</v>
+      </c>
+      <c r="B2345" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2345">
+        <v>0</v>
+      </c>
+      <c r="D2345">
+        <v>2831</v>
+      </c>
+      <c r="E2345">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2346">
+        <v>118</v>
+      </c>
+      <c r="B2346" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2346">
+        <v>0</v>
+      </c>
+      <c r="D2346">
+        <v>1011</v>
+      </c>
+      <c r="E2346">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2347">
+        <v>118</v>
+      </c>
+      <c r="B2347" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2347">
+        <v>0</v>
+      </c>
+      <c r="D2347">
+        <v>4041</v>
+      </c>
+      <c r="E2347">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2348">
+        <v>118</v>
+      </c>
+      <c r="B2348" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2348">
+        <v>0</v>
+      </c>
+      <c r="D2348">
+        <v>6708</v>
+      </c>
+      <c r="E2348">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2349">
+        <v>118</v>
+      </c>
+      <c r="B2349" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2349">
+        <v>0</v>
+      </c>
+      <c r="D2349">
+        <v>8768</v>
+      </c>
+      <c r="E2349">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2350">
+        <v>118</v>
+      </c>
+      <c r="B2350" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2350">
+        <v>0</v>
+      </c>
+      <c r="D2350">
+        <v>336</v>
+      </c>
+      <c r="E2350">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2351">
+        <v>118</v>
+      </c>
+      <c r="B2351" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2351">
+        <v>0</v>
+      </c>
+      <c r="D2351">
+        <v>2819</v>
+      </c>
+      <c r="E2351">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505A374F-8596-4BA7-B272-808215019B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4B4994-EA3E-4884-AB37-C858A8903C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2351"/>
+  <dimension ref="A1:T2361"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -41308,6 +41308,176 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2352" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2352">
+        <v>118</v>
+      </c>
+      <c r="B2352" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2352">
+        <v>1</v>
+      </c>
+      <c r="D2352">
+        <v>5354</v>
+      </c>
+      <c r="E2352">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2353">
+        <v>118</v>
+      </c>
+      <c r="B2353" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2353">
+        <v>1</v>
+      </c>
+      <c r="D2353">
+        <v>7161</v>
+      </c>
+      <c r="E2353">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2354">
+        <v>118</v>
+      </c>
+      <c r="B2354" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2354">
+        <v>1</v>
+      </c>
+      <c r="D2354">
+        <v>5777</v>
+      </c>
+      <c r="E2354">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2355">
+        <v>118</v>
+      </c>
+      <c r="B2355" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2355">
+        <v>1</v>
+      </c>
+      <c r="D2355">
+        <v>9215</v>
+      </c>
+      <c r="E2355">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2356">
+        <v>118</v>
+      </c>
+      <c r="B2356" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2356">
+        <v>1</v>
+      </c>
+      <c r="D2356">
+        <v>3145</v>
+      </c>
+      <c r="E2356">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2357">
+        <v>118</v>
+      </c>
+      <c r="B2357" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2357">
+        <v>1</v>
+      </c>
+      <c r="D2357">
+        <v>2537</v>
+      </c>
+      <c r="E2357">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2358">
+        <v>118</v>
+      </c>
+      <c r="B2358" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2358">
+        <v>1</v>
+      </c>
+      <c r="D2358">
+        <v>2349</v>
+      </c>
+      <c r="E2358">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2359">
+        <v>118</v>
+      </c>
+      <c r="B2359" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2359">
+        <v>1</v>
+      </c>
+      <c r="D2359">
+        <v>6278</v>
+      </c>
+      <c r="E2359">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2360">
+        <v>118</v>
+      </c>
+      <c r="B2360" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2360">
+        <v>1</v>
+      </c>
+      <c r="D2360">
+        <v>2937</v>
+      </c>
+      <c r="E2360">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2361">
+        <v>118</v>
+      </c>
+      <c r="B2361" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2361">
+        <v>1</v>
+      </c>
+      <c r="D2361">
+        <v>1334</v>
+      </c>
+      <c r="E2361">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4B4994-EA3E-4884-AB37-C858A8903C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26941D7-804D-4888-998E-13FCF16E70CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2361"/>
+  <dimension ref="A1:T2381"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -41478,6 +41478,346 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2362" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2362">
+        <v>119</v>
+      </c>
+      <c r="B2362" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2362">
+        <v>0</v>
+      </c>
+      <c r="D2362">
+        <v>6418</v>
+      </c>
+      <c r="E2362">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2363">
+        <v>119</v>
+      </c>
+      <c r="B2363" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2363">
+        <v>0</v>
+      </c>
+      <c r="D2363">
+        <v>4211</v>
+      </c>
+      <c r="E2363">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2364">
+        <v>119</v>
+      </c>
+      <c r="B2364" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2364">
+        <v>0</v>
+      </c>
+      <c r="D2364">
+        <v>1811</v>
+      </c>
+      <c r="E2364">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2365">
+        <v>119</v>
+      </c>
+      <c r="B2365" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2365">
+        <v>0</v>
+      </c>
+      <c r="D2365">
+        <v>5563</v>
+      </c>
+      <c r="E2365">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2366">
+        <v>119</v>
+      </c>
+      <c r="B2366" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2366">
+        <v>0</v>
+      </c>
+      <c r="D2366">
+        <v>1821</v>
+      </c>
+      <c r="E2366">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2367">
+        <v>119</v>
+      </c>
+      <c r="B2367" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2367">
+        <v>0</v>
+      </c>
+      <c r="D2367">
+        <v>9057</v>
+      </c>
+      <c r="E2367">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2368">
+        <v>119</v>
+      </c>
+      <c r="B2368" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2368">
+        <v>0</v>
+      </c>
+      <c r="D2368">
+        <v>8181</v>
+      </c>
+      <c r="E2368">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2369">
+        <v>119</v>
+      </c>
+      <c r="B2369" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2369">
+        <v>0</v>
+      </c>
+      <c r="D2369">
+        <v>9671</v>
+      </c>
+      <c r="E2369">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2370">
+        <v>119</v>
+      </c>
+      <c r="B2370" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2370">
+        <v>0</v>
+      </c>
+      <c r="D2370">
+        <v>8850</v>
+      </c>
+      <c r="E2370">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2371">
+        <v>119</v>
+      </c>
+      <c r="B2371" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2371">
+        <v>0</v>
+      </c>
+      <c r="D2371">
+        <v>4769</v>
+      </c>
+      <c r="E2371">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2372">
+        <v>119</v>
+      </c>
+      <c r="B2372" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2372">
+        <v>1</v>
+      </c>
+      <c r="D2372">
+        <v>2915</v>
+      </c>
+      <c r="E2372">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2373">
+        <v>119</v>
+      </c>
+      <c r="B2373" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2373">
+        <v>1</v>
+      </c>
+      <c r="D2373">
+        <v>8569</v>
+      </c>
+      <c r="E2373">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2374">
+        <v>119</v>
+      </c>
+      <c r="B2374" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2374">
+        <v>1</v>
+      </c>
+      <c r="D2374">
+        <v>2222</v>
+      </c>
+      <c r="E2374">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2375">
+        <v>119</v>
+      </c>
+      <c r="B2375" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2375">
+        <v>1</v>
+      </c>
+      <c r="D2375">
+        <v>9331</v>
+      </c>
+      <c r="E2375">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2376">
+        <v>119</v>
+      </c>
+      <c r="B2376" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2376">
+        <v>1</v>
+      </c>
+      <c r="D2376">
+        <v>5980</v>
+      </c>
+      <c r="E2376">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2377">
+        <v>119</v>
+      </c>
+      <c r="B2377" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2377">
+        <v>1</v>
+      </c>
+      <c r="D2377">
+        <v>5306</v>
+      </c>
+      <c r="E2377">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2378">
+        <v>119</v>
+      </c>
+      <c r="B2378" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2378">
+        <v>1</v>
+      </c>
+      <c r="D2378">
+        <v>197</v>
+      </c>
+      <c r="E2378">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2379">
+        <v>119</v>
+      </c>
+      <c r="B2379" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2379">
+        <v>1</v>
+      </c>
+      <c r="D2379">
+        <v>1371</v>
+      </c>
+      <c r="E2379">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2380">
+        <v>119</v>
+      </c>
+      <c r="B2380" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2380">
+        <v>1</v>
+      </c>
+      <c r="D2380">
+        <v>358</v>
+      </c>
+      <c r="E2380">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2381">
+        <v>119</v>
+      </c>
+      <c r="B2381" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2381">
+        <v>1</v>
+      </c>
+      <c r="D2381">
+        <v>3760</v>
+      </c>
+      <c r="E2381">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E26941D7-804D-4888-998E-13FCF16E70CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FF47EC-0994-4848-898B-BF9E3C599EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2381"/>
+  <dimension ref="A1:T2401"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -41818,6 +41818,346 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2382" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2382">
+        <v>120</v>
+      </c>
+      <c r="B2382" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2382">
+        <v>0</v>
+      </c>
+      <c r="D2382">
+        <v>9670</v>
+      </c>
+      <c r="E2382">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2383">
+        <v>120</v>
+      </c>
+      <c r="B2383" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2383">
+        <v>0</v>
+      </c>
+      <c r="D2383">
+        <v>6040</v>
+      </c>
+      <c r="E2383">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2384">
+        <v>120</v>
+      </c>
+      <c r="B2384" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2384">
+        <v>0</v>
+      </c>
+      <c r="D2384">
+        <v>7866</v>
+      </c>
+      <c r="E2384">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2385">
+        <v>120</v>
+      </c>
+      <c r="B2385" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2385">
+        <v>0</v>
+      </c>
+      <c r="D2385">
+        <v>7406</v>
+      </c>
+      <c r="E2385">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2386">
+        <v>120</v>
+      </c>
+      <c r="B2386" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2386">
+        <v>0</v>
+      </c>
+      <c r="D2386">
+        <v>2544</v>
+      </c>
+      <c r="E2386">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2387">
+        <v>120</v>
+      </c>
+      <c r="B2387" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2387">
+        <v>0</v>
+      </c>
+      <c r="D2387">
+        <v>6235</v>
+      </c>
+      <c r="E2387">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2388">
+        <v>120</v>
+      </c>
+      <c r="B2388" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2388">
+        <v>0</v>
+      </c>
+      <c r="D2388">
+        <v>2867</v>
+      </c>
+      <c r="E2388">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2389">
+        <v>120</v>
+      </c>
+      <c r="B2389" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2389">
+        <v>0</v>
+      </c>
+      <c r="D2389">
+        <v>745</v>
+      </c>
+      <c r="E2389">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2390">
+        <v>120</v>
+      </c>
+      <c r="B2390" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2390">
+        <v>0</v>
+      </c>
+      <c r="D2390">
+        <v>1826</v>
+      </c>
+      <c r="E2390">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2391">
+        <v>120</v>
+      </c>
+      <c r="B2391" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2391">
+        <v>0</v>
+      </c>
+      <c r="D2391">
+        <v>1803</v>
+      </c>
+      <c r="E2391">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2392">
+        <v>120</v>
+      </c>
+      <c r="B2392" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2392">
+        <v>1</v>
+      </c>
+      <c r="D2392">
+        <v>5713</v>
+      </c>
+      <c r="E2392">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2393">
+        <v>120</v>
+      </c>
+      <c r="B2393" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2393">
+        <v>1</v>
+      </c>
+      <c r="D2393">
+        <v>9448</v>
+      </c>
+      <c r="E2393">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2394">
+        <v>120</v>
+      </c>
+      <c r="B2394" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2394">
+        <v>1</v>
+      </c>
+      <c r="D2394">
+        <v>8583</v>
+      </c>
+      <c r="E2394">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2395">
+        <v>120</v>
+      </c>
+      <c r="B2395" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2395">
+        <v>1</v>
+      </c>
+      <c r="D2395">
+        <v>1025</v>
+      </c>
+      <c r="E2395">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2396">
+        <v>120</v>
+      </c>
+      <c r="B2396" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2396">
+        <v>1</v>
+      </c>
+      <c r="D2396">
+        <v>9469</v>
+      </c>
+      <c r="E2396">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2397">
+        <v>120</v>
+      </c>
+      <c r="B2397" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2397">
+        <v>1</v>
+      </c>
+      <c r="D2397">
+        <v>622</v>
+      </c>
+      <c r="E2397">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2398">
+        <v>120</v>
+      </c>
+      <c r="B2398" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2398">
+        <v>1</v>
+      </c>
+      <c r="D2398">
+        <v>6181</v>
+      </c>
+      <c r="E2398">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2399">
+        <v>120</v>
+      </c>
+      <c r="B2399" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2399">
+        <v>1</v>
+      </c>
+      <c r="D2399">
+        <v>7575</v>
+      </c>
+      <c r="E2399">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2400">
+        <v>120</v>
+      </c>
+      <c r="B2400" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2400">
+        <v>1</v>
+      </c>
+      <c r="D2400">
+        <v>5861</v>
+      </c>
+      <c r="E2400">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2401">
+        <v>120</v>
+      </c>
+      <c r="B2401" s="10">
+        <v>46042</v>
+      </c>
+      <c r="C2401">
+        <v>1</v>
+      </c>
+      <c r="D2401">
+        <v>2170</v>
+      </c>
+      <c r="E2401">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FF47EC-0994-4848-898B-BF9E3C599EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761CFDEE-E747-4B5B-9041-DB4C5BFF962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2401"/>
+  <dimension ref="A1:T2481"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -42158,6 +42158,1366 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2402" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2402">
+        <v>121</v>
+      </c>
+      <c r="B2402" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2402">
+        <v>0</v>
+      </c>
+      <c r="D2402">
+        <v>5412</v>
+      </c>
+      <c r="E2402">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2403">
+        <v>121</v>
+      </c>
+      <c r="B2403" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2403">
+        <v>0</v>
+      </c>
+      <c r="D2403">
+        <v>6633</v>
+      </c>
+      <c r="E2403">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2404">
+        <v>121</v>
+      </c>
+      <c r="B2404" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2404">
+        <v>0</v>
+      </c>
+      <c r="D2404">
+        <v>7748</v>
+      </c>
+      <c r="E2404">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2405">
+        <v>121</v>
+      </c>
+      <c r="B2405" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2405">
+        <v>0</v>
+      </c>
+      <c r="D2405">
+        <v>5583</v>
+      </c>
+      <c r="E2405">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2406">
+        <v>121</v>
+      </c>
+      <c r="B2406" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2406">
+        <v>0</v>
+      </c>
+      <c r="D2406">
+        <v>3530</v>
+      </c>
+      <c r="E2406">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2407">
+        <v>121</v>
+      </c>
+      <c r="B2407" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2407">
+        <v>0</v>
+      </c>
+      <c r="D2407">
+        <v>8815</v>
+      </c>
+      <c r="E2407">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2408">
+        <v>121</v>
+      </c>
+      <c r="B2408" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2408">
+        <v>0</v>
+      </c>
+      <c r="D2408">
+        <v>5900</v>
+      </c>
+      <c r="E2408">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2409">
+        <v>121</v>
+      </c>
+      <c r="B2409" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2409">
+        <v>0</v>
+      </c>
+      <c r="D2409">
+        <v>3029</v>
+      </c>
+      <c r="E2409">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2410">
+        <v>121</v>
+      </c>
+      <c r="B2410" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2410">
+        <v>0</v>
+      </c>
+      <c r="D2410">
+        <v>2947</v>
+      </c>
+      <c r="E2410">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2411">
+        <v>121</v>
+      </c>
+      <c r="B2411" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2411">
+        <v>0</v>
+      </c>
+      <c r="D2411">
+        <v>4530</v>
+      </c>
+      <c r="E2411">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2412">
+        <v>121</v>
+      </c>
+      <c r="B2412" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2412">
+        <v>1</v>
+      </c>
+      <c r="D2412">
+        <v>5804</v>
+      </c>
+      <c r="E2412">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2413">
+        <v>121</v>
+      </c>
+      <c r="B2413" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2413">
+        <v>1</v>
+      </c>
+      <c r="D2413">
+        <v>4714</v>
+      </c>
+      <c r="E2413">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2414">
+        <v>121</v>
+      </c>
+      <c r="B2414" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2414">
+        <v>1</v>
+      </c>
+      <c r="D2414">
+        <v>2446</v>
+      </c>
+      <c r="E2414">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2415">
+        <v>121</v>
+      </c>
+      <c r="B2415" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2415">
+        <v>1</v>
+      </c>
+      <c r="D2415">
+        <v>6976</v>
+      </c>
+      <c r="E2415">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2416">
+        <v>121</v>
+      </c>
+      <c r="B2416" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2416">
+        <v>1</v>
+      </c>
+      <c r="D2416">
+        <v>227</v>
+      </c>
+      <c r="E2416">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2417">
+        <v>121</v>
+      </c>
+      <c r="B2417" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2417">
+        <v>1</v>
+      </c>
+      <c r="D2417">
+        <v>605</v>
+      </c>
+      <c r="E2417">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2418">
+        <v>121</v>
+      </c>
+      <c r="B2418" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2418">
+        <v>1</v>
+      </c>
+      <c r="D2418">
+        <v>2683</v>
+      </c>
+      <c r="E2418">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2419">
+        <v>121</v>
+      </c>
+      <c r="B2419" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2419">
+        <v>1</v>
+      </c>
+      <c r="D2419">
+        <v>62</v>
+      </c>
+      <c r="E2419">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2420">
+        <v>121</v>
+      </c>
+      <c r="B2420" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2420">
+        <v>1</v>
+      </c>
+      <c r="D2420">
+        <v>929</v>
+      </c>
+      <c r="E2420">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2421">
+        <v>121</v>
+      </c>
+      <c r="B2421" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C2421">
+        <v>1</v>
+      </c>
+      <c r="D2421">
+        <v>8790</v>
+      </c>
+      <c r="E2421">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2422">
+        <v>122</v>
+      </c>
+      <c r="B2422" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2422">
+        <v>0</v>
+      </c>
+      <c r="D2422">
+        <v>894</v>
+      </c>
+      <c r="E2422">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2423">
+        <v>122</v>
+      </c>
+      <c r="B2423" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2423">
+        <v>0</v>
+      </c>
+      <c r="D2423">
+        <v>3852</v>
+      </c>
+      <c r="E2423">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2424">
+        <v>122</v>
+      </c>
+      <c r="B2424" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2424">
+        <v>0</v>
+      </c>
+      <c r="D2424">
+        <v>2927</v>
+      </c>
+      <c r="E2424">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2425">
+        <v>122</v>
+      </c>
+      <c r="B2425" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2425">
+        <v>0</v>
+      </c>
+      <c r="D2425">
+        <v>7281</v>
+      </c>
+      <c r="E2425">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2426">
+        <v>122</v>
+      </c>
+      <c r="B2426" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2426">
+        <v>0</v>
+      </c>
+      <c r="D2426">
+        <v>40</v>
+      </c>
+      <c r="E2426">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2427">
+        <v>122</v>
+      </c>
+      <c r="B2427" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2427">
+        <v>0</v>
+      </c>
+      <c r="D2427">
+        <v>5007</v>
+      </c>
+      <c r="E2427">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2428">
+        <v>122</v>
+      </c>
+      <c r="B2428" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2428">
+        <v>0</v>
+      </c>
+      <c r="D2428">
+        <v>5680</v>
+      </c>
+      <c r="E2428">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2429">
+        <v>122</v>
+      </c>
+      <c r="B2429" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2429">
+        <v>0</v>
+      </c>
+      <c r="D2429">
+        <v>5289</v>
+      </c>
+      <c r="E2429">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2430">
+        <v>122</v>
+      </c>
+      <c r="B2430" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2430">
+        <v>0</v>
+      </c>
+      <c r="D2430">
+        <v>8584</v>
+      </c>
+      <c r="E2430">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2431">
+        <v>122</v>
+      </c>
+      <c r="B2431" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2431">
+        <v>0</v>
+      </c>
+      <c r="D2431">
+        <v>5955</v>
+      </c>
+      <c r="E2431">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2432">
+        <v>122</v>
+      </c>
+      <c r="B2432" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2432">
+        <v>1</v>
+      </c>
+      <c r="D2432">
+        <v>7975</v>
+      </c>
+      <c r="E2432">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2433">
+        <v>122</v>
+      </c>
+      <c r="B2433" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2433">
+        <v>1</v>
+      </c>
+      <c r="D2433">
+        <v>3130</v>
+      </c>
+      <c r="E2433">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2434">
+        <v>122</v>
+      </c>
+      <c r="B2434" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2434">
+        <v>1</v>
+      </c>
+      <c r="D2434">
+        <v>3896</v>
+      </c>
+      <c r="E2434">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2435">
+        <v>122</v>
+      </c>
+      <c r="B2435" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2435">
+        <v>1</v>
+      </c>
+      <c r="D2435">
+        <v>3658</v>
+      </c>
+      <c r="E2435">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2436">
+        <v>122</v>
+      </c>
+      <c r="B2436" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2436">
+        <v>1</v>
+      </c>
+      <c r="D2436">
+        <v>5518</v>
+      </c>
+      <c r="E2436">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2437">
+        <v>122</v>
+      </c>
+      <c r="B2437" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2437">
+        <v>1</v>
+      </c>
+      <c r="D2437">
+        <v>6598</v>
+      </c>
+      <c r="E2437">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2438">
+        <v>122</v>
+      </c>
+      <c r="B2438" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2438">
+        <v>1</v>
+      </c>
+      <c r="D2438">
+        <v>5497</v>
+      </c>
+      <c r="E2438">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2439">
+        <v>122</v>
+      </c>
+      <c r="B2439" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2439">
+        <v>1</v>
+      </c>
+      <c r="D2439">
+        <v>5013</v>
+      </c>
+      <c r="E2439">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2440">
+        <v>122</v>
+      </c>
+      <c r="B2440" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2440">
+        <v>1</v>
+      </c>
+      <c r="D2440">
+        <v>6067</v>
+      </c>
+      <c r="E2440">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2441">
+        <v>122</v>
+      </c>
+      <c r="B2441" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C2441">
+        <v>1</v>
+      </c>
+      <c r="D2441">
+        <v>5960</v>
+      </c>
+      <c r="E2441">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2442">
+        <v>123</v>
+      </c>
+      <c r="B2442" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2442">
+        <v>0</v>
+      </c>
+      <c r="D2442">
+        <v>8800</v>
+      </c>
+      <c r="E2442">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2443">
+        <v>123</v>
+      </c>
+      <c r="B2443" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2443">
+        <v>0</v>
+      </c>
+      <c r="D2443">
+        <v>635</v>
+      </c>
+      <c r="E2443">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2444">
+        <v>123</v>
+      </c>
+      <c r="B2444" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2444">
+        <v>0</v>
+      </c>
+      <c r="D2444">
+        <v>9942</v>
+      </c>
+      <c r="E2444">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2445">
+        <v>123</v>
+      </c>
+      <c r="B2445" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2445">
+        <v>0</v>
+      </c>
+      <c r="D2445">
+        <v>5610</v>
+      </c>
+      <c r="E2445">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2446">
+        <v>123</v>
+      </c>
+      <c r="B2446" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2446">
+        <v>0</v>
+      </c>
+      <c r="D2446">
+        <v>259</v>
+      </c>
+      <c r="E2446">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2447">
+        <v>123</v>
+      </c>
+      <c r="B2447" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2447">
+        <v>0</v>
+      </c>
+      <c r="D2447">
+        <v>8798</v>
+      </c>
+      <c r="E2447">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2448">
+        <v>123</v>
+      </c>
+      <c r="B2448" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2448">
+        <v>0</v>
+      </c>
+      <c r="D2448">
+        <v>28</v>
+      </c>
+      <c r="E2448">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2449">
+        <v>123</v>
+      </c>
+      <c r="B2449" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2449">
+        <v>0</v>
+      </c>
+      <c r="D2449">
+        <v>1654</v>
+      </c>
+      <c r="E2449">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2450">
+        <v>123</v>
+      </c>
+      <c r="B2450" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2450">
+        <v>0</v>
+      </c>
+      <c r="D2450">
+        <v>1054</v>
+      </c>
+      <c r="E2450">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2451">
+        <v>123</v>
+      </c>
+      <c r="B2451" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2451">
+        <v>0</v>
+      </c>
+      <c r="D2451">
+        <v>8169</v>
+      </c>
+      <c r="E2451">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2452">
+        <v>123</v>
+      </c>
+      <c r="B2452" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2452">
+        <v>1</v>
+      </c>
+      <c r="D2452">
+        <v>5487</v>
+      </c>
+      <c r="E2452">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2453">
+        <v>123</v>
+      </c>
+      <c r="B2453" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2453">
+        <v>1</v>
+      </c>
+      <c r="D2453">
+        <v>922</v>
+      </c>
+      <c r="E2453">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2454">
+        <v>123</v>
+      </c>
+      <c r="B2454" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2454">
+        <v>1</v>
+      </c>
+      <c r="D2454">
+        <v>8568</v>
+      </c>
+      <c r="E2454">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2455">
+        <v>123</v>
+      </c>
+      <c r="B2455" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2455">
+        <v>1</v>
+      </c>
+      <c r="D2455">
+        <v>7254</v>
+      </c>
+      <c r="E2455">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2456">
+        <v>123</v>
+      </c>
+      <c r="B2456" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2456">
+        <v>1</v>
+      </c>
+      <c r="D2456">
+        <v>9479</v>
+      </c>
+      <c r="E2456">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2457">
+        <v>123</v>
+      </c>
+      <c r="B2457" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2457">
+        <v>1</v>
+      </c>
+      <c r="D2457">
+        <v>2233</v>
+      </c>
+      <c r="E2457">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2458">
+        <v>123</v>
+      </c>
+      <c r="B2458" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2458">
+        <v>1</v>
+      </c>
+      <c r="D2458">
+        <v>4070</v>
+      </c>
+      <c r="E2458">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2459">
+        <v>123</v>
+      </c>
+      <c r="B2459" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2459">
+        <v>1</v>
+      </c>
+      <c r="D2459">
+        <v>174</v>
+      </c>
+      <c r="E2459">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2460">
+        <v>123</v>
+      </c>
+      <c r="B2460" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2460">
+        <v>1</v>
+      </c>
+      <c r="D2460">
+        <v>896</v>
+      </c>
+      <c r="E2460">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2461">
+        <v>123</v>
+      </c>
+      <c r="B2461" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C2461">
+        <v>1</v>
+      </c>
+      <c r="D2461">
+        <v>8470</v>
+      </c>
+      <c r="E2461">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2462">
+        <v>124</v>
+      </c>
+      <c r="B2462" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2462">
+        <v>0</v>
+      </c>
+      <c r="D2462">
+        <v>619</v>
+      </c>
+      <c r="E2462">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2463">
+        <v>124</v>
+      </c>
+      <c r="B2463" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2463">
+        <v>0</v>
+      </c>
+      <c r="D2463">
+        <v>9005</v>
+      </c>
+      <c r="E2463">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2464">
+        <v>124</v>
+      </c>
+      <c r="B2464" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2464">
+        <v>0</v>
+      </c>
+      <c r="D2464">
+        <v>3735</v>
+      </c>
+      <c r="E2464">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2465">
+        <v>124</v>
+      </c>
+      <c r="B2465" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2465">
+        <v>0</v>
+      </c>
+      <c r="D2465">
+        <v>828</v>
+      </c>
+      <c r="E2465">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2466">
+        <v>124</v>
+      </c>
+      <c r="B2466" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2466">
+        <v>0</v>
+      </c>
+      <c r="D2466">
+        <v>6042</v>
+      </c>
+      <c r="E2466">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2467">
+        <v>124</v>
+      </c>
+      <c r="B2467" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2467">
+        <v>0</v>
+      </c>
+      <c r="D2467">
+        <v>5067</v>
+      </c>
+      <c r="E2467">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2468">
+        <v>124</v>
+      </c>
+      <c r="B2468" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2468">
+        <v>0</v>
+      </c>
+      <c r="D2468">
+        <v>2078</v>
+      </c>
+      <c r="E2468">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2469">
+        <v>124</v>
+      </c>
+      <c r="B2469" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2469">
+        <v>0</v>
+      </c>
+      <c r="D2469">
+        <v>843</v>
+      </c>
+      <c r="E2469">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2470">
+        <v>124</v>
+      </c>
+      <c r="B2470" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2470">
+        <v>0</v>
+      </c>
+      <c r="D2470">
+        <v>3019</v>
+      </c>
+      <c r="E2470">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2471">
+        <v>124</v>
+      </c>
+      <c r="B2471" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2471">
+        <v>0</v>
+      </c>
+      <c r="D2471">
+        <v>3973</v>
+      </c>
+      <c r="E2471">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2472">
+        <v>124</v>
+      </c>
+      <c r="B2472" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2472">
+        <v>1</v>
+      </c>
+      <c r="D2472">
+        <v>3122</v>
+      </c>
+      <c r="E2472">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2473">
+        <v>124</v>
+      </c>
+      <c r="B2473" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2473">
+        <v>1</v>
+      </c>
+      <c r="D2473">
+        <v>2115</v>
+      </c>
+      <c r="E2473">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2474">
+        <v>124</v>
+      </c>
+      <c r="B2474" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2474">
+        <v>1</v>
+      </c>
+      <c r="D2474">
+        <v>1765</v>
+      </c>
+      <c r="E2474">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2475">
+        <v>124</v>
+      </c>
+      <c r="B2475" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2475">
+        <v>1</v>
+      </c>
+      <c r="D2475">
+        <v>4479</v>
+      </c>
+      <c r="E2475">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2476">
+        <v>124</v>
+      </c>
+      <c r="B2476" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2476">
+        <v>1</v>
+      </c>
+      <c r="D2476">
+        <v>8512</v>
+      </c>
+      <c r="E2476">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2477">
+        <v>124</v>
+      </c>
+      <c r="B2477" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2477">
+        <v>1</v>
+      </c>
+      <c r="D2477">
+        <v>4100</v>
+      </c>
+      <c r="E2477">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2478">
+        <v>124</v>
+      </c>
+      <c r="B2478" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2478">
+        <v>1</v>
+      </c>
+      <c r="D2478">
+        <v>5088</v>
+      </c>
+      <c r="E2478">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2479">
+        <v>124</v>
+      </c>
+      <c r="B2479" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2479">
+        <v>1</v>
+      </c>
+      <c r="D2479">
+        <v>8503</v>
+      </c>
+      <c r="E2479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2480">
+        <v>124</v>
+      </c>
+      <c r="B2480" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2480">
+        <v>1</v>
+      </c>
+      <c r="D2480">
+        <v>243</v>
+      </c>
+      <c r="E2480">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2481">
+        <v>124</v>
+      </c>
+      <c r="B2481" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C2481">
+        <v>1</v>
+      </c>
+      <c r="D2481">
+        <v>377</v>
+      </c>
+      <c r="E2481">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{761CFDEE-E747-4B5B-9041-DB4C5BFF962A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBA1CAF-F5F4-4817-B0B3-D6DBAD5B3DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2481"/>
+  <dimension ref="A1:T2501"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -43518,6 +43518,346 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2482" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2482">
+        <v>125</v>
+      </c>
+      <c r="B2482" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2482">
+        <v>0</v>
+      </c>
+      <c r="D2482">
+        <v>2053</v>
+      </c>
+      <c r="E2482">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2483">
+        <v>125</v>
+      </c>
+      <c r="B2483" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2483">
+        <v>0</v>
+      </c>
+      <c r="D2483">
+        <v>1817</v>
+      </c>
+      <c r="E2483">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2484">
+        <v>125</v>
+      </c>
+      <c r="B2484" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2484">
+        <v>0</v>
+      </c>
+      <c r="D2484">
+        <v>1981</v>
+      </c>
+      <c r="E2484">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2485">
+        <v>125</v>
+      </c>
+      <c r="B2485" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2485">
+        <v>0</v>
+      </c>
+      <c r="D2485">
+        <v>5094</v>
+      </c>
+      <c r="E2485">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2486">
+        <v>125</v>
+      </c>
+      <c r="B2486" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2486">
+        <v>0</v>
+      </c>
+      <c r="D2486">
+        <v>8106</v>
+      </c>
+      <c r="E2486">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2487">
+        <v>125</v>
+      </c>
+      <c r="B2487" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2487">
+        <v>0</v>
+      </c>
+      <c r="D2487">
+        <v>3184</v>
+      </c>
+      <c r="E2487">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2488">
+        <v>125</v>
+      </c>
+      <c r="B2488" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2488">
+        <v>0</v>
+      </c>
+      <c r="D2488">
+        <v>1533</v>
+      </c>
+      <c r="E2488">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2489">
+        <v>125</v>
+      </c>
+      <c r="B2489" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2489">
+        <v>0</v>
+      </c>
+      <c r="D2489">
+        <v>1143</v>
+      </c>
+      <c r="E2489">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2490">
+        <v>125</v>
+      </c>
+      <c r="B2490" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2490">
+        <v>0</v>
+      </c>
+      <c r="D2490">
+        <v>9496</v>
+      </c>
+      <c r="E2490">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2491">
+        <v>125</v>
+      </c>
+      <c r="B2491" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2491">
+        <v>0</v>
+      </c>
+      <c r="D2491">
+        <v>4005</v>
+      </c>
+      <c r="E2491">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2492">
+        <v>125</v>
+      </c>
+      <c r="B2492" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2492">
+        <v>1</v>
+      </c>
+      <c r="D2492" s="11">
+        <v>2477</v>
+      </c>
+      <c r="E2492" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2493">
+        <v>125</v>
+      </c>
+      <c r="B2493" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2493">
+        <v>1</v>
+      </c>
+      <c r="D2493" s="12">
+        <v>6270</v>
+      </c>
+      <c r="E2493" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2494">
+        <v>125</v>
+      </c>
+      <c r="B2494" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2494">
+        <v>1</v>
+      </c>
+      <c r="D2494" s="11">
+        <v>3943</v>
+      </c>
+      <c r="E2494" s="11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2495">
+        <v>125</v>
+      </c>
+      <c r="B2495" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2495">
+        <v>1</v>
+      </c>
+      <c r="D2495" s="12">
+        <v>7958</v>
+      </c>
+      <c r="E2495" s="12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2496">
+        <v>125</v>
+      </c>
+      <c r="B2496" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2496">
+        <v>1</v>
+      </c>
+      <c r="D2496" s="11">
+        <v>4909</v>
+      </c>
+      <c r="E2496" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2497">
+        <v>125</v>
+      </c>
+      <c r="B2497" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2497">
+        <v>1</v>
+      </c>
+      <c r="D2497" s="12">
+        <v>9370</v>
+      </c>
+      <c r="E2497" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2498">
+        <v>125</v>
+      </c>
+      <c r="B2498" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2498">
+        <v>1</v>
+      </c>
+      <c r="D2498" s="11">
+        <v>2330</v>
+      </c>
+      <c r="E2498" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2499">
+        <v>125</v>
+      </c>
+      <c r="B2499" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2499">
+        <v>1</v>
+      </c>
+      <c r="D2499" s="12">
+        <v>7003</v>
+      </c>
+      <c r="E2499" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2500">
+        <v>125</v>
+      </c>
+      <c r="B2500" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2500">
+        <v>1</v>
+      </c>
+      <c r="D2500" s="11">
+        <v>9197</v>
+      </c>
+      <c r="E2500" s="11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2501">
+        <v>125</v>
+      </c>
+      <c r="B2501" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C2501">
+        <v>1</v>
+      </c>
+      <c r="D2501" s="13">
+        <v>1284</v>
+      </c>
+      <c r="E2501" s="13">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBBA1CAF-F5F4-4817-B0B3-D6DBAD5B3DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814795FD-2584-4AFD-B0B9-F875308494D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2501"/>
+  <dimension ref="A1:T2520"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -43671,7 +43671,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2491" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2491">
         <v>125</v>
       </c>
@@ -43688,7 +43688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2492" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2492">
         <v>125</v>
       </c>
@@ -43698,14 +43698,14 @@
       <c r="C2492">
         <v>1</v>
       </c>
-      <c r="D2492" s="11">
+      <c r="D2492">
         <v>2477</v>
       </c>
-      <c r="E2492" s="11">
+      <c r="E2492">
         <v>20</v>
       </c>
     </row>
-    <row r="2493" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2493">
         <v>125</v>
       </c>
@@ -43715,14 +43715,14 @@
       <c r="C2493">
         <v>1</v>
       </c>
-      <c r="D2493" s="12">
+      <c r="D2493">
         <v>6270</v>
       </c>
-      <c r="E2493" s="12">
+      <c r="E2493">
         <v>18</v>
       </c>
     </row>
-    <row r="2494" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2494">
         <v>125</v>
       </c>
@@ -43732,14 +43732,14 @@
       <c r="C2494">
         <v>1</v>
       </c>
-      <c r="D2494" s="11">
+      <c r="D2494">
         <v>3943</v>
       </c>
-      <c r="E2494" s="11">
+      <c r="E2494">
         <v>11</v>
       </c>
     </row>
-    <row r="2495" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2495">
         <v>125</v>
       </c>
@@ -43749,14 +43749,14 @@
       <c r="C2495">
         <v>1</v>
       </c>
-      <c r="D2495" s="12">
+      <c r="D2495">
         <v>7958</v>
       </c>
-      <c r="E2495" s="12">
+      <c r="E2495">
         <v>15</v>
       </c>
     </row>
-    <row r="2496" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2496">
         <v>125</v>
       </c>
@@ -43766,14 +43766,14 @@
       <c r="C2496">
         <v>1</v>
       </c>
-      <c r="D2496" s="11">
+      <c r="D2496">
         <v>4909</v>
       </c>
-      <c r="E2496" s="11">
+      <c r="E2496">
         <v>3</v>
       </c>
     </row>
-    <row r="2497" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2497">
         <v>125</v>
       </c>
@@ -43783,14 +43783,14 @@
       <c r="C2497">
         <v>1</v>
       </c>
-      <c r="D2497" s="12">
+      <c r="D2497">
         <v>9370</v>
       </c>
-      <c r="E2497" s="12">
+      <c r="E2497">
         <v>18</v>
       </c>
     </row>
-    <row r="2498" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2498">
         <v>125</v>
       </c>
@@ -43800,14 +43800,14 @@
       <c r="C2498">
         <v>1</v>
       </c>
-      <c r="D2498" s="11">
+      <c r="D2498">
         <v>2330</v>
       </c>
-      <c r="E2498" s="11">
+      <c r="E2498">
         <v>8</v>
       </c>
     </row>
-    <row r="2499" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2499">
         <v>125</v>
       </c>
@@ -43817,14 +43817,14 @@
       <c r="C2499">
         <v>1</v>
       </c>
-      <c r="D2499" s="12">
+      <c r="D2499">
         <v>7003</v>
       </c>
-      <c r="E2499" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2500" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E2499">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2500">
         <v>125</v>
       </c>
@@ -43834,14 +43834,14 @@
       <c r="C2500">
         <v>1</v>
       </c>
-      <c r="D2500" s="11">
+      <c r="D2500">
         <v>9197</v>
       </c>
-      <c r="E2500" s="11">
+      <c r="E2500">
         <v>25</v>
       </c>
     </row>
-    <row r="2501" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2501">
         <v>125</v>
       </c>
@@ -43851,11 +43851,334 @@
       <c r="C2501">
         <v>1</v>
       </c>
-      <c r="D2501" s="13">
+      <c r="D2501">
         <v>1284</v>
       </c>
-      <c r="E2501" s="13">
+      <c r="E2501">
         <v>21</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2502">
+        <v>126</v>
+      </c>
+      <c r="B2502" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2502">
+        <v>0</v>
+      </c>
+      <c r="D2502">
+        <v>6370</v>
+      </c>
+      <c r="E2502">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2503">
+        <v>126</v>
+      </c>
+      <c r="B2503" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2503">
+        <v>0</v>
+      </c>
+      <c r="D2503">
+        <v>1682</v>
+      </c>
+      <c r="E2503">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2504">
+        <v>126</v>
+      </c>
+      <c r="B2504" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2504">
+        <v>0</v>
+      </c>
+      <c r="D2504">
+        <v>1618</v>
+      </c>
+      <c r="E2504">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2505">
+        <v>126</v>
+      </c>
+      <c r="B2505" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2505">
+        <v>0</v>
+      </c>
+      <c r="D2505">
+        <v>5890</v>
+      </c>
+      <c r="E2505">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2506">
+        <v>126</v>
+      </c>
+      <c r="B2506" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2506">
+        <v>0</v>
+      </c>
+      <c r="D2506">
+        <v>3548</v>
+      </c>
+      <c r="E2506">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2507">
+        <v>126</v>
+      </c>
+      <c r="B2507" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2507">
+        <v>0</v>
+      </c>
+      <c r="D2507">
+        <v>8031</v>
+      </c>
+      <c r="E2507">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2508">
+        <v>126</v>
+      </c>
+      <c r="B2508" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2508">
+        <v>0</v>
+      </c>
+      <c r="D2508">
+        <v>2391</v>
+      </c>
+      <c r="E2508">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2509">
+        <v>126</v>
+      </c>
+      <c r="B2509" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2509">
+        <v>0</v>
+      </c>
+      <c r="D2509">
+        <v>8811</v>
+      </c>
+      <c r="E2509">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2510">
+        <v>126</v>
+      </c>
+      <c r="B2510" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2510">
+        <v>0</v>
+      </c>
+      <c r="D2510">
+        <v>8762</v>
+      </c>
+      <c r="E2510">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2511">
+        <v>126</v>
+      </c>
+      <c r="B2511" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2511">
+        <v>1</v>
+      </c>
+      <c r="D2511">
+        <v>1326</v>
+      </c>
+      <c r="E2511">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2512">
+        <v>126</v>
+      </c>
+      <c r="B2512" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2512">
+        <v>1</v>
+      </c>
+      <c r="D2512">
+        <v>8815</v>
+      </c>
+      <c r="E2512">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2513">
+        <v>126</v>
+      </c>
+      <c r="B2513" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2513">
+        <v>1</v>
+      </c>
+      <c r="D2513">
+        <v>1114</v>
+      </c>
+      <c r="E2513">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2514">
+        <v>126</v>
+      </c>
+      <c r="B2514" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2514">
+        <v>1</v>
+      </c>
+      <c r="D2514">
+        <v>9377</v>
+      </c>
+      <c r="E2514">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2515">
+        <v>126</v>
+      </c>
+      <c r="B2515" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2515">
+        <v>1</v>
+      </c>
+      <c r="D2515">
+        <v>228</v>
+      </c>
+      <c r="E2515">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2516">
+        <v>126</v>
+      </c>
+      <c r="B2516" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2516">
+        <v>1</v>
+      </c>
+      <c r="D2516">
+        <v>5561</v>
+      </c>
+      <c r="E2516">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2517">
+        <v>126</v>
+      </c>
+      <c r="B2517" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2517">
+        <v>1</v>
+      </c>
+      <c r="D2517">
+        <v>9191</v>
+      </c>
+      <c r="E2517">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2518">
+        <v>126</v>
+      </c>
+      <c r="B2518" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2518">
+        <v>1</v>
+      </c>
+      <c r="D2518">
+        <v>7949</v>
+      </c>
+      <c r="E2518">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2519">
+        <v>126</v>
+      </c>
+      <c r="B2519" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2519">
+        <v>1</v>
+      </c>
+      <c r="D2519">
+        <v>7972</v>
+      </c>
+      <c r="E2519">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2520">
+        <v>126</v>
+      </c>
+      <c r="B2520" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C2520">
+        <v>1</v>
+      </c>
+      <c r="D2520">
+        <v>7263</v>
+      </c>
+      <c r="E2520">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{814795FD-2584-4AFD-B0B9-F875308494D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114750DE-4962-48ED-BE14-8164FC175CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2520"/>
+  <dimension ref="A1:T2600"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -44181,6 +44181,1366 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2521" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2521">
+        <v>127</v>
+      </c>
+      <c r="B2521" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2521">
+        <v>0</v>
+      </c>
+      <c r="D2521">
+        <v>7384</v>
+      </c>
+      <c r="E2521">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2522">
+        <v>127</v>
+      </c>
+      <c r="B2522" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2522">
+        <v>0</v>
+      </c>
+      <c r="D2522">
+        <v>1595</v>
+      </c>
+      <c r="E2522">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2523">
+        <v>127</v>
+      </c>
+      <c r="B2523" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2523">
+        <v>0</v>
+      </c>
+      <c r="D2523">
+        <v>1221</v>
+      </c>
+      <c r="E2523">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2524">
+        <v>127</v>
+      </c>
+      <c r="B2524" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2524">
+        <v>0</v>
+      </c>
+      <c r="D2524">
+        <v>9896</v>
+      </c>
+      <c r="E2524">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2525">
+        <v>127</v>
+      </c>
+      <c r="B2525" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2525">
+        <v>0</v>
+      </c>
+      <c r="D2525">
+        <v>2902</v>
+      </c>
+      <c r="E2525">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2526">
+        <v>127</v>
+      </c>
+      <c r="B2526" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2526">
+        <v>0</v>
+      </c>
+      <c r="D2526">
+        <v>1602</v>
+      </c>
+      <c r="E2526">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2527">
+        <v>127</v>
+      </c>
+      <c r="B2527" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2527">
+        <v>0</v>
+      </c>
+      <c r="D2527">
+        <v>4286</v>
+      </c>
+      <c r="E2527">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2528">
+        <v>127</v>
+      </c>
+      <c r="B2528" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2528">
+        <v>0</v>
+      </c>
+      <c r="D2528">
+        <v>6772</v>
+      </c>
+      <c r="E2528">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2529">
+        <v>127</v>
+      </c>
+      <c r="B2529" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2529">
+        <v>0</v>
+      </c>
+      <c r="D2529">
+        <v>6380</v>
+      </c>
+      <c r="E2529">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2530">
+        <v>127</v>
+      </c>
+      <c r="B2530" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2530">
+        <v>0</v>
+      </c>
+      <c r="D2530">
+        <v>9380</v>
+      </c>
+      <c r="E2530">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2531">
+        <v>127</v>
+      </c>
+      <c r="B2531" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2531">
+        <v>1</v>
+      </c>
+      <c r="D2531">
+        <v>9043</v>
+      </c>
+      <c r="E2531">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2532">
+        <v>127</v>
+      </c>
+      <c r="B2532" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2532">
+        <v>1</v>
+      </c>
+      <c r="D2532">
+        <v>4709</v>
+      </c>
+      <c r="E2532">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2533">
+        <v>127</v>
+      </c>
+      <c r="B2533" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2533">
+        <v>1</v>
+      </c>
+      <c r="D2533">
+        <v>9631</v>
+      </c>
+      <c r="E2533">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2534">
+        <v>127</v>
+      </c>
+      <c r="B2534" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2534">
+        <v>1</v>
+      </c>
+      <c r="D2534">
+        <v>1758</v>
+      </c>
+      <c r="E2534">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2535">
+        <v>127</v>
+      </c>
+      <c r="B2535" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2535">
+        <v>1</v>
+      </c>
+      <c r="D2535">
+        <v>7218</v>
+      </c>
+      <c r="E2535">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2536">
+        <v>127</v>
+      </c>
+      <c r="B2536" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2536">
+        <v>1</v>
+      </c>
+      <c r="D2536">
+        <v>2620</v>
+      </c>
+      <c r="E2536">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2537">
+        <v>127</v>
+      </c>
+      <c r="B2537" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2537">
+        <v>1</v>
+      </c>
+      <c r="D2537">
+        <v>2966</v>
+      </c>
+      <c r="E2537">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2538">
+        <v>127</v>
+      </c>
+      <c r="B2538" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2538">
+        <v>1</v>
+      </c>
+      <c r="D2538">
+        <v>2611</v>
+      </c>
+      <c r="E2538">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2539">
+        <v>127</v>
+      </c>
+      <c r="B2539" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2539">
+        <v>1</v>
+      </c>
+      <c r="D2539">
+        <v>5596</v>
+      </c>
+      <c r="E2539">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2540">
+        <v>127</v>
+      </c>
+      <c r="B2540" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C2540">
+        <v>1</v>
+      </c>
+      <c r="D2540">
+        <v>3092</v>
+      </c>
+      <c r="E2540">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2541">
+        <v>128</v>
+      </c>
+      <c r="B2541" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2541">
+        <v>0</v>
+      </c>
+      <c r="D2541">
+        <v>6346</v>
+      </c>
+      <c r="E2541">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2542">
+        <v>128</v>
+      </c>
+      <c r="B2542" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2542">
+        <v>0</v>
+      </c>
+      <c r="D2542">
+        <v>9722</v>
+      </c>
+      <c r="E2542">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2543">
+        <v>128</v>
+      </c>
+      <c r="B2543" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2543">
+        <v>0</v>
+      </c>
+      <c r="D2543">
+        <v>6666</v>
+      </c>
+      <c r="E2543">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2544">
+        <v>128</v>
+      </c>
+      <c r="B2544" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2544">
+        <v>0</v>
+      </c>
+      <c r="D2544">
+        <v>8204</v>
+      </c>
+      <c r="E2544">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2545">
+        <v>128</v>
+      </c>
+      <c r="B2545" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2545">
+        <v>0</v>
+      </c>
+      <c r="D2545">
+        <v>9273</v>
+      </c>
+      <c r="E2545">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2546">
+        <v>128</v>
+      </c>
+      <c r="B2546" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2546">
+        <v>0</v>
+      </c>
+      <c r="D2546">
+        <v>65</v>
+      </c>
+      <c r="E2546">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2547">
+        <v>128</v>
+      </c>
+      <c r="B2547" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2547">
+        <v>0</v>
+      </c>
+      <c r="D2547">
+        <v>6085</v>
+      </c>
+      <c r="E2547">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2548">
+        <v>128</v>
+      </c>
+      <c r="B2548" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2548">
+        <v>0</v>
+      </c>
+      <c r="D2548">
+        <v>8956</v>
+      </c>
+      <c r="E2548">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2549">
+        <v>128</v>
+      </c>
+      <c r="B2549" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2549">
+        <v>0</v>
+      </c>
+      <c r="D2549">
+        <v>6712</v>
+      </c>
+      <c r="E2549">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2550">
+        <v>128</v>
+      </c>
+      <c r="B2550" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2550">
+        <v>0</v>
+      </c>
+      <c r="D2550">
+        <v>2478</v>
+      </c>
+      <c r="E2550">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2551">
+        <v>128</v>
+      </c>
+      <c r="B2551" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2551">
+        <v>1</v>
+      </c>
+      <c r="D2551">
+        <v>9753</v>
+      </c>
+      <c r="E2551">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2552">
+        <v>128</v>
+      </c>
+      <c r="B2552" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2552">
+        <v>1</v>
+      </c>
+      <c r="D2552">
+        <v>4687</v>
+      </c>
+      <c r="E2552">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2553">
+        <v>128</v>
+      </c>
+      <c r="B2553" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2553">
+        <v>1</v>
+      </c>
+      <c r="D2553">
+        <v>9515</v>
+      </c>
+      <c r="E2553">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2554">
+        <v>128</v>
+      </c>
+      <c r="B2554" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2554">
+        <v>1</v>
+      </c>
+      <c r="D2554">
+        <v>5996</v>
+      </c>
+      <c r="E2554">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2555">
+        <v>128</v>
+      </c>
+      <c r="B2555" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2555">
+        <v>1</v>
+      </c>
+      <c r="D2555">
+        <v>6303</v>
+      </c>
+      <c r="E2555">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2556">
+        <v>128</v>
+      </c>
+      <c r="B2556" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2556">
+        <v>1</v>
+      </c>
+      <c r="D2556">
+        <v>9258</v>
+      </c>
+      <c r="E2556">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2557">
+        <v>128</v>
+      </c>
+      <c r="B2557" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2557">
+        <v>1</v>
+      </c>
+      <c r="D2557">
+        <v>436</v>
+      </c>
+      <c r="E2557">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2558">
+        <v>128</v>
+      </c>
+      <c r="B2558" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2558">
+        <v>1</v>
+      </c>
+      <c r="D2558">
+        <v>620</v>
+      </c>
+      <c r="E2558">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2559">
+        <v>128</v>
+      </c>
+      <c r="B2559" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2559">
+        <v>1</v>
+      </c>
+      <c r="D2559">
+        <v>9008</v>
+      </c>
+      <c r="E2559">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2560">
+        <v>128</v>
+      </c>
+      <c r="B2560" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C2560">
+        <v>1</v>
+      </c>
+      <c r="D2560">
+        <v>7080</v>
+      </c>
+      <c r="E2560">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2561">
+        <v>129</v>
+      </c>
+      <c r="B2561" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2561">
+        <v>0</v>
+      </c>
+      <c r="D2561">
+        <v>9172</v>
+      </c>
+      <c r="E2561">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2562">
+        <v>129</v>
+      </c>
+      <c r="B2562" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2562">
+        <v>0</v>
+      </c>
+      <c r="D2562">
+        <v>1368</v>
+      </c>
+      <c r="E2562">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2563">
+        <v>129</v>
+      </c>
+      <c r="B2563" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2563">
+        <v>0</v>
+      </c>
+      <c r="D2563">
+        <v>7720</v>
+      </c>
+      <c r="E2563">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2564">
+        <v>129</v>
+      </c>
+      <c r="B2564" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2564">
+        <v>0</v>
+      </c>
+      <c r="D2564">
+        <v>1622</v>
+      </c>
+      <c r="E2564">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2565">
+        <v>129</v>
+      </c>
+      <c r="B2565" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2565">
+        <v>0</v>
+      </c>
+      <c r="D2565">
+        <v>8306</v>
+      </c>
+      <c r="E2565">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2566">
+        <v>129</v>
+      </c>
+      <c r="B2566" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2566">
+        <v>0</v>
+      </c>
+      <c r="D2566">
+        <v>2227</v>
+      </c>
+      <c r="E2566">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2567">
+        <v>129</v>
+      </c>
+      <c r="B2567" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2567">
+        <v>0</v>
+      </c>
+      <c r="D2567">
+        <v>9527</v>
+      </c>
+      <c r="E2567">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2568">
+        <v>129</v>
+      </c>
+      <c r="B2568" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2568">
+        <v>0</v>
+      </c>
+      <c r="D2568">
+        <v>6534</v>
+      </c>
+      <c r="E2568">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2569">
+        <v>129</v>
+      </c>
+      <c r="B2569" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2569">
+        <v>0</v>
+      </c>
+      <c r="D2569">
+        <v>7564</v>
+      </c>
+      <c r="E2569">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2570">
+        <v>129</v>
+      </c>
+      <c r="B2570" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2570">
+        <v>0</v>
+      </c>
+      <c r="D2570">
+        <v>4182</v>
+      </c>
+      <c r="E2570">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2571">
+        <v>129</v>
+      </c>
+      <c r="B2571" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2571">
+        <v>1</v>
+      </c>
+      <c r="D2571">
+        <v>3248</v>
+      </c>
+      <c r="E2571">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2572">
+        <v>129</v>
+      </c>
+      <c r="B2572" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2572">
+        <v>1</v>
+      </c>
+      <c r="D2572">
+        <v>211</v>
+      </c>
+      <c r="E2572">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2573">
+        <v>129</v>
+      </c>
+      <c r="B2573" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2573">
+        <v>1</v>
+      </c>
+      <c r="D2573">
+        <v>1817</v>
+      </c>
+      <c r="E2573">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2574">
+        <v>129</v>
+      </c>
+      <c r="B2574" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2574">
+        <v>1</v>
+      </c>
+      <c r="D2574">
+        <v>244</v>
+      </c>
+      <c r="E2574">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2575">
+        <v>129</v>
+      </c>
+      <c r="B2575" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2575">
+        <v>1</v>
+      </c>
+      <c r="D2575">
+        <v>8190</v>
+      </c>
+      <c r="E2575">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2576">
+        <v>129</v>
+      </c>
+      <c r="B2576" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2576">
+        <v>1</v>
+      </c>
+      <c r="D2576">
+        <v>1360</v>
+      </c>
+      <c r="E2576">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2577">
+        <v>129</v>
+      </c>
+      <c r="B2577" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2577">
+        <v>1</v>
+      </c>
+      <c r="D2577">
+        <v>4335</v>
+      </c>
+      <c r="E2577">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2578">
+        <v>129</v>
+      </c>
+      <c r="B2578" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2578">
+        <v>1</v>
+      </c>
+      <c r="D2578">
+        <v>7017</v>
+      </c>
+      <c r="E2578">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2579">
+        <v>129</v>
+      </c>
+      <c r="B2579" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2579">
+        <v>1</v>
+      </c>
+      <c r="D2579">
+        <v>1445</v>
+      </c>
+      <c r="E2579">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2580">
+        <v>129</v>
+      </c>
+      <c r="B2580" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C2580">
+        <v>1</v>
+      </c>
+      <c r="D2580">
+        <v>1476</v>
+      </c>
+      <c r="E2580">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2581">
+        <v>130</v>
+      </c>
+      <c r="B2581" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2581">
+        <v>0</v>
+      </c>
+      <c r="D2581">
+        <v>2457</v>
+      </c>
+      <c r="E2581">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2582">
+        <v>130</v>
+      </c>
+      <c r="B2582" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2582">
+        <v>0</v>
+      </c>
+      <c r="D2582">
+        <v>6296</v>
+      </c>
+      <c r="E2582">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2583">
+        <v>130</v>
+      </c>
+      <c r="B2583" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2583">
+        <v>0</v>
+      </c>
+      <c r="D2583">
+        <v>7873</v>
+      </c>
+      <c r="E2583">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2584">
+        <v>130</v>
+      </c>
+      <c r="B2584" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2584">
+        <v>0</v>
+      </c>
+      <c r="D2584">
+        <v>4926</v>
+      </c>
+      <c r="E2584">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2585">
+        <v>130</v>
+      </c>
+      <c r="B2585" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2585">
+        <v>0</v>
+      </c>
+      <c r="D2585">
+        <v>3125</v>
+      </c>
+      <c r="E2585">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2586">
+        <v>130</v>
+      </c>
+      <c r="B2586" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2586">
+        <v>0</v>
+      </c>
+      <c r="D2586">
+        <v>9687</v>
+      </c>
+      <c r="E2586">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2587">
+        <v>130</v>
+      </c>
+      <c r="B2587" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2587">
+        <v>0</v>
+      </c>
+      <c r="D2587">
+        <v>2379</v>
+      </c>
+      <c r="E2587">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2588">
+        <v>130</v>
+      </c>
+      <c r="B2588" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2588">
+        <v>0</v>
+      </c>
+      <c r="D2588">
+        <v>8508</v>
+      </c>
+      <c r="E2588">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2589">
+        <v>130</v>
+      </c>
+      <c r="B2589" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2589">
+        <v>0</v>
+      </c>
+      <c r="D2589">
+        <v>6188</v>
+      </c>
+      <c r="E2589">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2590">
+        <v>130</v>
+      </c>
+      <c r="B2590" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2590">
+        <v>0</v>
+      </c>
+      <c r="D2590">
+        <v>1888</v>
+      </c>
+      <c r="E2590">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2591">
+        <v>130</v>
+      </c>
+      <c r="B2591" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2591">
+        <v>1</v>
+      </c>
+      <c r="D2591">
+        <v>295</v>
+      </c>
+      <c r="E2591">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2592">
+        <v>130</v>
+      </c>
+      <c r="B2592" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2592">
+        <v>1</v>
+      </c>
+      <c r="D2592">
+        <v>6984</v>
+      </c>
+      <c r="E2592">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2593">
+        <v>130</v>
+      </c>
+      <c r="B2593" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2593">
+        <v>1</v>
+      </c>
+      <c r="D2593">
+        <v>8710</v>
+      </c>
+      <c r="E2593">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2594">
+        <v>130</v>
+      </c>
+      <c r="B2594" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2594">
+        <v>1</v>
+      </c>
+      <c r="D2594">
+        <v>870</v>
+      </c>
+      <c r="E2594">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2595">
+        <v>130</v>
+      </c>
+      <c r="B2595" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2595">
+        <v>1</v>
+      </c>
+      <c r="D2595">
+        <v>8206</v>
+      </c>
+      <c r="E2595">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2596">
+        <v>130</v>
+      </c>
+      <c r="B2596" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2596">
+        <v>1</v>
+      </c>
+      <c r="D2596">
+        <v>1928</v>
+      </c>
+      <c r="E2596">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2597">
+        <v>130</v>
+      </c>
+      <c r="B2597" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2597">
+        <v>1</v>
+      </c>
+      <c r="D2597">
+        <v>8451</v>
+      </c>
+      <c r="E2597">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2598">
+        <v>130</v>
+      </c>
+      <c r="B2598" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2598">
+        <v>1</v>
+      </c>
+      <c r="D2598">
+        <v>6326</v>
+      </c>
+      <c r="E2598">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2599">
+        <v>130</v>
+      </c>
+      <c r="B2599" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2599">
+        <v>1</v>
+      </c>
+      <c r="D2599">
+        <v>4344</v>
+      </c>
+      <c r="E2599">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2600">
+        <v>130</v>
+      </c>
+      <c r="B2600" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C2600">
+        <v>1</v>
+      </c>
+      <c r="D2600">
+        <v>3515</v>
+      </c>
+      <c r="E2600">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\jogodobicho\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114750DE-4962-48ED-BE14-8164FC175CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3AB105-B635-40A8-B19E-9E86176782EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2600"/>
+  <dimension ref="A1:T2321"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -40798,4749 +40798,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2322" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2322">
-        <v>117</v>
-      </c>
-      <c r="B2322" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2322">
-        <v>0</v>
-      </c>
-      <c r="D2322">
-        <v>9471</v>
-      </c>
-      <c r="E2322">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2323" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2323">
-        <v>117</v>
-      </c>
-      <c r="B2323" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2323">
-        <v>0</v>
-      </c>
-      <c r="D2323">
-        <v>5902</v>
-      </c>
-      <c r="E2323">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2324" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2324">
-        <v>117</v>
-      </c>
-      <c r="B2324" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2324">
-        <v>0</v>
-      </c>
-      <c r="D2324">
-        <v>5958</v>
-      </c>
-      <c r="E2324">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2325" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2325">
-        <v>117</v>
-      </c>
-      <c r="B2325" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2325">
-        <v>0</v>
-      </c>
-      <c r="D2325">
-        <v>5794</v>
-      </c>
-      <c r="E2325">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2326" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2326">
-        <v>117</v>
-      </c>
-      <c r="B2326" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2326">
-        <v>0</v>
-      </c>
-      <c r="D2326">
-        <v>8434</v>
-      </c>
-      <c r="E2326">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2327" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2327">
-        <v>117</v>
-      </c>
-      <c r="B2327" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2327">
-        <v>0</v>
-      </c>
-      <c r="D2327">
-        <v>9170</v>
-      </c>
-      <c r="E2327">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2328" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2328">
-        <v>117</v>
-      </c>
-      <c r="B2328" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2328">
-        <v>0</v>
-      </c>
-      <c r="D2328">
-        <v>8408</v>
-      </c>
-      <c r="E2328">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2329" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2329">
-        <v>117</v>
-      </c>
-      <c r="B2329" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2329">
-        <v>0</v>
-      </c>
-      <c r="D2329">
-        <v>2593</v>
-      </c>
-      <c r="E2329">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2330" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2330">
-        <v>117</v>
-      </c>
-      <c r="B2330" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2330">
-        <v>0</v>
-      </c>
-      <c r="D2330">
-        <v>3100</v>
-      </c>
-      <c r="E2330">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2331" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2331">
-        <v>117</v>
-      </c>
-      <c r="B2331" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2331">
-        <v>0</v>
-      </c>
-      <c r="D2331">
-        <v>5856</v>
-      </c>
-      <c r="E2331">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2332" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2332">
-        <v>117</v>
-      </c>
-      <c r="B2332" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2332">
-        <v>1</v>
-      </c>
-      <c r="D2332">
-        <v>2371</v>
-      </c>
-      <c r="E2332">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2333" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2333">
-        <v>117</v>
-      </c>
-      <c r="B2333" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2333">
-        <v>1</v>
-      </c>
-      <c r="D2333">
-        <v>4266</v>
-      </c>
-      <c r="E2333">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2334" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2334">
-        <v>117</v>
-      </c>
-      <c r="B2334" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2334">
-        <v>1</v>
-      </c>
-      <c r="D2334">
-        <v>9275</v>
-      </c>
-      <c r="E2334">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2335" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2335">
-        <v>117</v>
-      </c>
-      <c r="B2335" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2335">
-        <v>1</v>
-      </c>
-      <c r="D2335">
-        <v>6352</v>
-      </c>
-      <c r="E2335">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2336" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2336">
-        <v>117</v>
-      </c>
-      <c r="B2336" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2336">
-        <v>1</v>
-      </c>
-      <c r="D2336">
-        <v>4087</v>
-      </c>
-      <c r="E2336">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2337" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2337">
-        <v>117</v>
-      </c>
-      <c r="B2337" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2337">
-        <v>1</v>
-      </c>
-      <c r="D2337">
-        <v>6793</v>
-      </c>
-      <c r="E2337">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2338" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2338">
-        <v>117</v>
-      </c>
-      <c r="B2338" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2338">
-        <v>1</v>
-      </c>
-      <c r="D2338">
-        <v>8109</v>
-      </c>
-      <c r="E2338">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2339" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2339">
-        <v>117</v>
-      </c>
-      <c r="B2339" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2339">
-        <v>1</v>
-      </c>
-      <c r="D2339">
-        <v>101</v>
-      </c>
-      <c r="E2339">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2340" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2340">
-        <v>117</v>
-      </c>
-      <c r="B2340" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2340">
-        <v>1</v>
-      </c>
-      <c r="D2340">
-        <v>6727</v>
-      </c>
-      <c r="E2340">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2341" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2341">
-        <v>117</v>
-      </c>
-      <c r="B2341" s="10">
-        <v>46038</v>
-      </c>
-      <c r="C2341">
-        <v>1</v>
-      </c>
-      <c r="D2341">
-        <v>9688</v>
-      </c>
-      <c r="E2341">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2342" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2342">
-        <v>118</v>
-      </c>
-      <c r="B2342" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2342">
-        <v>0</v>
-      </c>
-      <c r="D2342">
-        <v>4855</v>
-      </c>
-      <c r="E2342">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2343" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2343">
-        <v>118</v>
-      </c>
-      <c r="B2343" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2343">
-        <v>0</v>
-      </c>
-      <c r="D2343">
-        <v>7141</v>
-      </c>
-      <c r="E2343">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2344" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2344">
-        <v>118</v>
-      </c>
-      <c r="B2344" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2344">
-        <v>0</v>
-      </c>
-      <c r="D2344">
-        <v>4432</v>
-      </c>
-      <c r="E2344">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2345" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2345">
-        <v>118</v>
-      </c>
-      <c r="B2345" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2345">
-        <v>0</v>
-      </c>
-      <c r="D2345">
-        <v>2831</v>
-      </c>
-      <c r="E2345">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2346" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2346">
-        <v>118</v>
-      </c>
-      <c r="B2346" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2346">
-        <v>0</v>
-      </c>
-      <c r="D2346">
-        <v>1011</v>
-      </c>
-      <c r="E2346">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2347" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2347">
-        <v>118</v>
-      </c>
-      <c r="B2347" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2347">
-        <v>0</v>
-      </c>
-      <c r="D2347">
-        <v>4041</v>
-      </c>
-      <c r="E2347">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2348" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2348">
-        <v>118</v>
-      </c>
-      <c r="B2348" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2348">
-        <v>0</v>
-      </c>
-      <c r="D2348">
-        <v>6708</v>
-      </c>
-      <c r="E2348">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2349" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2349">
-        <v>118</v>
-      </c>
-      <c r="B2349" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2349">
-        <v>0</v>
-      </c>
-      <c r="D2349">
-        <v>8768</v>
-      </c>
-      <c r="E2349">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2350" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2350">
-        <v>118</v>
-      </c>
-      <c r="B2350" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2350">
-        <v>0</v>
-      </c>
-      <c r="D2350">
-        <v>336</v>
-      </c>
-      <c r="E2350">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2351" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2351">
-        <v>118</v>
-      </c>
-      <c r="B2351" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2351">
-        <v>0</v>
-      </c>
-      <c r="D2351">
-        <v>2819</v>
-      </c>
-      <c r="E2351">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2352" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2352">
-        <v>118</v>
-      </c>
-      <c r="B2352" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2352">
-        <v>1</v>
-      </c>
-      <c r="D2352">
-        <v>5354</v>
-      </c>
-      <c r="E2352">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2353" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2353">
-        <v>118</v>
-      </c>
-      <c r="B2353" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2353">
-        <v>1</v>
-      </c>
-      <c r="D2353">
-        <v>7161</v>
-      </c>
-      <c r="E2353">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2354" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2354">
-        <v>118</v>
-      </c>
-      <c r="B2354" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2354">
-        <v>1</v>
-      </c>
-      <c r="D2354">
-        <v>5777</v>
-      </c>
-      <c r="E2354">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2355" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2355">
-        <v>118</v>
-      </c>
-      <c r="B2355" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2355">
-        <v>1</v>
-      </c>
-      <c r="D2355">
-        <v>9215</v>
-      </c>
-      <c r="E2355">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2356" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2356">
-        <v>118</v>
-      </c>
-      <c r="B2356" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2356">
-        <v>1</v>
-      </c>
-      <c r="D2356">
-        <v>3145</v>
-      </c>
-      <c r="E2356">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2357" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2357">
-        <v>118</v>
-      </c>
-      <c r="B2357" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2357">
-        <v>1</v>
-      </c>
-      <c r="D2357">
-        <v>2537</v>
-      </c>
-      <c r="E2357">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2358" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2358">
-        <v>118</v>
-      </c>
-      <c r="B2358" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2358">
-        <v>1</v>
-      </c>
-      <c r="D2358">
-        <v>2349</v>
-      </c>
-      <c r="E2358">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2359" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2359">
-        <v>118</v>
-      </c>
-      <c r="B2359" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2359">
-        <v>1</v>
-      </c>
-      <c r="D2359">
-        <v>6278</v>
-      </c>
-      <c r="E2359">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2360" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2360">
-        <v>118</v>
-      </c>
-      <c r="B2360" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2360">
-        <v>1</v>
-      </c>
-      <c r="D2360">
-        <v>2937</v>
-      </c>
-      <c r="E2360">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2361" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2361">
-        <v>118</v>
-      </c>
-      <c r="B2361" s="10">
-        <v>46039</v>
-      </c>
-      <c r="C2361">
-        <v>1</v>
-      </c>
-      <c r="D2361">
-        <v>1334</v>
-      </c>
-      <c r="E2361">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2362" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2362">
-        <v>119</v>
-      </c>
-      <c r="B2362" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2362">
-        <v>0</v>
-      </c>
-      <c r="D2362">
-        <v>6418</v>
-      </c>
-      <c r="E2362">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2363" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2363">
-        <v>119</v>
-      </c>
-      <c r="B2363" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2363">
-        <v>0</v>
-      </c>
-      <c r="D2363">
-        <v>4211</v>
-      </c>
-      <c r="E2363">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2364" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2364">
-        <v>119</v>
-      </c>
-      <c r="B2364" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2364">
-        <v>0</v>
-      </c>
-      <c r="D2364">
-        <v>1811</v>
-      </c>
-      <c r="E2364">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2365" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2365">
-        <v>119</v>
-      </c>
-      <c r="B2365" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2365">
-        <v>0</v>
-      </c>
-      <c r="D2365">
-        <v>5563</v>
-      </c>
-      <c r="E2365">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2366" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2366">
-        <v>119</v>
-      </c>
-      <c r="B2366" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2366">
-        <v>0</v>
-      </c>
-      <c r="D2366">
-        <v>1821</v>
-      </c>
-      <c r="E2366">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2367" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2367">
-        <v>119</v>
-      </c>
-      <c r="B2367" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2367">
-        <v>0</v>
-      </c>
-      <c r="D2367">
-        <v>9057</v>
-      </c>
-      <c r="E2367">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2368" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2368">
-        <v>119</v>
-      </c>
-      <c r="B2368" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2368">
-        <v>0</v>
-      </c>
-      <c r="D2368">
-        <v>8181</v>
-      </c>
-      <c r="E2368">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2369" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2369">
-        <v>119</v>
-      </c>
-      <c r="B2369" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2369">
-        <v>0</v>
-      </c>
-      <c r="D2369">
-        <v>9671</v>
-      </c>
-      <c r="E2369">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2370" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2370">
-        <v>119</v>
-      </c>
-      <c r="B2370" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2370">
-        <v>0</v>
-      </c>
-      <c r="D2370">
-        <v>8850</v>
-      </c>
-      <c r="E2370">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2371" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2371">
-        <v>119</v>
-      </c>
-      <c r="B2371" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2371">
-        <v>0</v>
-      </c>
-      <c r="D2371">
-        <v>4769</v>
-      </c>
-      <c r="E2371">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2372" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2372">
-        <v>119</v>
-      </c>
-      <c r="B2372" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2372">
-        <v>1</v>
-      </c>
-      <c r="D2372">
-        <v>2915</v>
-      </c>
-      <c r="E2372">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2373" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2373">
-        <v>119</v>
-      </c>
-      <c r="B2373" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2373">
-        <v>1</v>
-      </c>
-      <c r="D2373">
-        <v>8569</v>
-      </c>
-      <c r="E2373">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2374" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2374">
-        <v>119</v>
-      </c>
-      <c r="B2374" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2374">
-        <v>1</v>
-      </c>
-      <c r="D2374">
-        <v>2222</v>
-      </c>
-      <c r="E2374">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2375" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2375">
-        <v>119</v>
-      </c>
-      <c r="B2375" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2375">
-        <v>1</v>
-      </c>
-      <c r="D2375">
-        <v>9331</v>
-      </c>
-      <c r="E2375">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2376" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2376">
-        <v>119</v>
-      </c>
-      <c r="B2376" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2376">
-        <v>1</v>
-      </c>
-      <c r="D2376">
-        <v>5980</v>
-      </c>
-      <c r="E2376">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2377" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2377">
-        <v>119</v>
-      </c>
-      <c r="B2377" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2377">
-        <v>1</v>
-      </c>
-      <c r="D2377">
-        <v>5306</v>
-      </c>
-      <c r="E2377">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2378" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2378">
-        <v>119</v>
-      </c>
-      <c r="B2378" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2378">
-        <v>1</v>
-      </c>
-      <c r="D2378">
-        <v>197</v>
-      </c>
-      <c r="E2378">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2379" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2379">
-        <v>119</v>
-      </c>
-      <c r="B2379" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2379">
-        <v>1</v>
-      </c>
-      <c r="D2379">
-        <v>1371</v>
-      </c>
-      <c r="E2379">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2380" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2380">
-        <v>119</v>
-      </c>
-      <c r="B2380" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2380">
-        <v>1</v>
-      </c>
-      <c r="D2380">
-        <v>358</v>
-      </c>
-      <c r="E2380">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2381" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2381">
-        <v>119</v>
-      </c>
-      <c r="B2381" s="10">
-        <v>46041</v>
-      </c>
-      <c r="C2381">
-        <v>1</v>
-      </c>
-      <c r="D2381">
-        <v>3760</v>
-      </c>
-      <c r="E2381">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2382" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2382">
-        <v>120</v>
-      </c>
-      <c r="B2382" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2382">
-        <v>0</v>
-      </c>
-      <c r="D2382">
-        <v>9670</v>
-      </c>
-      <c r="E2382">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2383" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2383">
-        <v>120</v>
-      </c>
-      <c r="B2383" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2383">
-        <v>0</v>
-      </c>
-      <c r="D2383">
-        <v>6040</v>
-      </c>
-      <c r="E2383">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2384" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2384">
-        <v>120</v>
-      </c>
-      <c r="B2384" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2384">
-        <v>0</v>
-      </c>
-      <c r="D2384">
-        <v>7866</v>
-      </c>
-      <c r="E2384">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2385" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2385">
-        <v>120</v>
-      </c>
-      <c r="B2385" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2385">
-        <v>0</v>
-      </c>
-      <c r="D2385">
-        <v>7406</v>
-      </c>
-      <c r="E2385">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2386" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2386">
-        <v>120</v>
-      </c>
-      <c r="B2386" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2386">
-        <v>0</v>
-      </c>
-      <c r="D2386">
-        <v>2544</v>
-      </c>
-      <c r="E2386">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2387" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2387">
-        <v>120</v>
-      </c>
-      <c r="B2387" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2387">
-        <v>0</v>
-      </c>
-      <c r="D2387">
-        <v>6235</v>
-      </c>
-      <c r="E2387">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2388" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2388">
-        <v>120</v>
-      </c>
-      <c r="B2388" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2388">
-        <v>0</v>
-      </c>
-      <c r="D2388">
-        <v>2867</v>
-      </c>
-      <c r="E2388">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2389" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2389">
-        <v>120</v>
-      </c>
-      <c r="B2389" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2389">
-        <v>0</v>
-      </c>
-      <c r="D2389">
-        <v>745</v>
-      </c>
-      <c r="E2389">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2390" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2390">
-        <v>120</v>
-      </c>
-      <c r="B2390" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2390">
-        <v>0</v>
-      </c>
-      <c r="D2390">
-        <v>1826</v>
-      </c>
-      <c r="E2390">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2391" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2391">
-        <v>120</v>
-      </c>
-      <c r="B2391" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2391">
-        <v>0</v>
-      </c>
-      <c r="D2391">
-        <v>1803</v>
-      </c>
-      <c r="E2391">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2392" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2392">
-        <v>120</v>
-      </c>
-      <c r="B2392" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2392">
-        <v>1</v>
-      </c>
-      <c r="D2392">
-        <v>5713</v>
-      </c>
-      <c r="E2392">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2393" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2393">
-        <v>120</v>
-      </c>
-      <c r="B2393" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2393">
-        <v>1</v>
-      </c>
-      <c r="D2393">
-        <v>9448</v>
-      </c>
-      <c r="E2393">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2394" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2394">
-        <v>120</v>
-      </c>
-      <c r="B2394" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2394">
-        <v>1</v>
-      </c>
-      <c r="D2394">
-        <v>8583</v>
-      </c>
-      <c r="E2394">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2395" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2395">
-        <v>120</v>
-      </c>
-      <c r="B2395" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2395">
-        <v>1</v>
-      </c>
-      <c r="D2395">
-        <v>1025</v>
-      </c>
-      <c r="E2395">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2396" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2396">
-        <v>120</v>
-      </c>
-      <c r="B2396" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2396">
-        <v>1</v>
-      </c>
-      <c r="D2396">
-        <v>9469</v>
-      </c>
-      <c r="E2396">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2397" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2397">
-        <v>120</v>
-      </c>
-      <c r="B2397" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2397">
-        <v>1</v>
-      </c>
-      <c r="D2397">
-        <v>622</v>
-      </c>
-      <c r="E2397">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2398" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2398">
-        <v>120</v>
-      </c>
-      <c r="B2398" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2398">
-        <v>1</v>
-      </c>
-      <c r="D2398">
-        <v>6181</v>
-      </c>
-      <c r="E2398">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2399" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2399">
-        <v>120</v>
-      </c>
-      <c r="B2399" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2399">
-        <v>1</v>
-      </c>
-      <c r="D2399">
-        <v>7575</v>
-      </c>
-      <c r="E2399">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2400" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2400">
-        <v>120</v>
-      </c>
-      <c r="B2400" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2400">
-        <v>1</v>
-      </c>
-      <c r="D2400">
-        <v>5861</v>
-      </c>
-      <c r="E2400">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2401" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2401">
-        <v>120</v>
-      </c>
-      <c r="B2401" s="10">
-        <v>46042</v>
-      </c>
-      <c r="C2401">
-        <v>1</v>
-      </c>
-      <c r="D2401">
-        <v>2170</v>
-      </c>
-      <c r="E2401">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2402" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2402">
-        <v>121</v>
-      </c>
-      <c r="B2402" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2402">
-        <v>0</v>
-      </c>
-      <c r="D2402">
-        <v>5412</v>
-      </c>
-      <c r="E2402">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2403" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2403">
-        <v>121</v>
-      </c>
-      <c r="B2403" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2403">
-        <v>0</v>
-      </c>
-      <c r="D2403">
-        <v>6633</v>
-      </c>
-      <c r="E2403">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2404" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2404">
-        <v>121</v>
-      </c>
-      <c r="B2404" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2404">
-        <v>0</v>
-      </c>
-      <c r="D2404">
-        <v>7748</v>
-      </c>
-      <c r="E2404">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2405" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2405">
-        <v>121</v>
-      </c>
-      <c r="B2405" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2405">
-        <v>0</v>
-      </c>
-      <c r="D2405">
-        <v>5583</v>
-      </c>
-      <c r="E2405">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2406" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2406">
-        <v>121</v>
-      </c>
-      <c r="B2406" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2406">
-        <v>0</v>
-      </c>
-      <c r="D2406">
-        <v>3530</v>
-      </c>
-      <c r="E2406">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2407" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2407">
-        <v>121</v>
-      </c>
-      <c r="B2407" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2407">
-        <v>0</v>
-      </c>
-      <c r="D2407">
-        <v>8815</v>
-      </c>
-      <c r="E2407">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2408" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2408">
-        <v>121</v>
-      </c>
-      <c r="B2408" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2408">
-        <v>0</v>
-      </c>
-      <c r="D2408">
-        <v>5900</v>
-      </c>
-      <c r="E2408">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2409" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2409">
-        <v>121</v>
-      </c>
-      <c r="B2409" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2409">
-        <v>0</v>
-      </c>
-      <c r="D2409">
-        <v>3029</v>
-      </c>
-      <c r="E2409">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2410" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2410">
-        <v>121</v>
-      </c>
-      <c r="B2410" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2410">
-        <v>0</v>
-      </c>
-      <c r="D2410">
-        <v>2947</v>
-      </c>
-      <c r="E2410">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2411" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2411">
-        <v>121</v>
-      </c>
-      <c r="B2411" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2411">
-        <v>0</v>
-      </c>
-      <c r="D2411">
-        <v>4530</v>
-      </c>
-      <c r="E2411">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2412" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2412">
-        <v>121</v>
-      </c>
-      <c r="B2412" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2412">
-        <v>1</v>
-      </c>
-      <c r="D2412">
-        <v>5804</v>
-      </c>
-      <c r="E2412">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2413" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2413">
-        <v>121</v>
-      </c>
-      <c r="B2413" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2413">
-        <v>1</v>
-      </c>
-      <c r="D2413">
-        <v>4714</v>
-      </c>
-      <c r="E2413">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2414" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2414">
-        <v>121</v>
-      </c>
-      <c r="B2414" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2414">
-        <v>1</v>
-      </c>
-      <c r="D2414">
-        <v>2446</v>
-      </c>
-      <c r="E2414">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2415" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2415">
-        <v>121</v>
-      </c>
-      <c r="B2415" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2415">
-        <v>1</v>
-      </c>
-      <c r="D2415">
-        <v>6976</v>
-      </c>
-      <c r="E2415">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2416" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2416">
-        <v>121</v>
-      </c>
-      <c r="B2416" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2416">
-        <v>1</v>
-      </c>
-      <c r="D2416">
-        <v>227</v>
-      </c>
-      <c r="E2416">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2417" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2417">
-        <v>121</v>
-      </c>
-      <c r="B2417" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2417">
-        <v>1</v>
-      </c>
-      <c r="D2417">
-        <v>605</v>
-      </c>
-      <c r="E2417">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2418" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2418">
-        <v>121</v>
-      </c>
-      <c r="B2418" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2418">
-        <v>1</v>
-      </c>
-      <c r="D2418">
-        <v>2683</v>
-      </c>
-      <c r="E2418">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2419" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2419">
-        <v>121</v>
-      </c>
-      <c r="B2419" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2419">
-        <v>1</v>
-      </c>
-      <c r="D2419">
-        <v>62</v>
-      </c>
-      <c r="E2419">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2420" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2420">
-        <v>121</v>
-      </c>
-      <c r="B2420" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2420">
-        <v>1</v>
-      </c>
-      <c r="D2420">
-        <v>929</v>
-      </c>
-      <c r="E2420">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2421" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2421">
-        <v>121</v>
-      </c>
-      <c r="B2421" s="10">
-        <v>46043</v>
-      </c>
-      <c r="C2421">
-        <v>1</v>
-      </c>
-      <c r="D2421">
-        <v>8790</v>
-      </c>
-      <c r="E2421">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2422" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2422">
-        <v>122</v>
-      </c>
-      <c r="B2422" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2422">
-        <v>0</v>
-      </c>
-      <c r="D2422">
-        <v>894</v>
-      </c>
-      <c r="E2422">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2423" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2423">
-        <v>122</v>
-      </c>
-      <c r="B2423" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2423">
-        <v>0</v>
-      </c>
-      <c r="D2423">
-        <v>3852</v>
-      </c>
-      <c r="E2423">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2424" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2424">
-        <v>122</v>
-      </c>
-      <c r="B2424" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2424">
-        <v>0</v>
-      </c>
-      <c r="D2424">
-        <v>2927</v>
-      </c>
-      <c r="E2424">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2425" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2425">
-        <v>122</v>
-      </c>
-      <c r="B2425" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2425">
-        <v>0</v>
-      </c>
-      <c r="D2425">
-        <v>7281</v>
-      </c>
-      <c r="E2425">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2426" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2426">
-        <v>122</v>
-      </c>
-      <c r="B2426" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2426">
-        <v>0</v>
-      </c>
-      <c r="D2426">
-        <v>40</v>
-      </c>
-      <c r="E2426">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2427" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2427">
-        <v>122</v>
-      </c>
-      <c r="B2427" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2427">
-        <v>0</v>
-      </c>
-      <c r="D2427">
-        <v>5007</v>
-      </c>
-      <c r="E2427">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2428" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2428">
-        <v>122</v>
-      </c>
-      <c r="B2428" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2428">
-        <v>0</v>
-      </c>
-      <c r="D2428">
-        <v>5680</v>
-      </c>
-      <c r="E2428">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2429" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2429">
-        <v>122</v>
-      </c>
-      <c r="B2429" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2429">
-        <v>0</v>
-      </c>
-      <c r="D2429">
-        <v>5289</v>
-      </c>
-      <c r="E2429">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2430" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2430">
-        <v>122</v>
-      </c>
-      <c r="B2430" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2430">
-        <v>0</v>
-      </c>
-      <c r="D2430">
-        <v>8584</v>
-      </c>
-      <c r="E2430">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2431" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2431">
-        <v>122</v>
-      </c>
-      <c r="B2431" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2431">
-        <v>0</v>
-      </c>
-      <c r="D2431">
-        <v>5955</v>
-      </c>
-      <c r="E2431">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2432" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2432">
-        <v>122</v>
-      </c>
-      <c r="B2432" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2432">
-        <v>1</v>
-      </c>
-      <c r="D2432">
-        <v>7975</v>
-      </c>
-      <c r="E2432">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2433" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2433">
-        <v>122</v>
-      </c>
-      <c r="B2433" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2433">
-        <v>1</v>
-      </c>
-      <c r="D2433">
-        <v>3130</v>
-      </c>
-      <c r="E2433">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2434" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2434">
-        <v>122</v>
-      </c>
-      <c r="B2434" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2434">
-        <v>1</v>
-      </c>
-      <c r="D2434">
-        <v>3896</v>
-      </c>
-      <c r="E2434">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2435" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2435">
-        <v>122</v>
-      </c>
-      <c r="B2435" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2435">
-        <v>1</v>
-      </c>
-      <c r="D2435">
-        <v>3658</v>
-      </c>
-      <c r="E2435">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2436" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2436">
-        <v>122</v>
-      </c>
-      <c r="B2436" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2436">
-        <v>1</v>
-      </c>
-      <c r="D2436">
-        <v>5518</v>
-      </c>
-      <c r="E2436">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2437" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2437">
-        <v>122</v>
-      </c>
-      <c r="B2437" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2437">
-        <v>1</v>
-      </c>
-      <c r="D2437">
-        <v>6598</v>
-      </c>
-      <c r="E2437">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2438" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2438">
-        <v>122</v>
-      </c>
-      <c r="B2438" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2438">
-        <v>1</v>
-      </c>
-      <c r="D2438">
-        <v>5497</v>
-      </c>
-      <c r="E2438">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2439" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2439">
-        <v>122</v>
-      </c>
-      <c r="B2439" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2439">
-        <v>1</v>
-      </c>
-      <c r="D2439">
-        <v>5013</v>
-      </c>
-      <c r="E2439">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2440" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2440">
-        <v>122</v>
-      </c>
-      <c r="B2440" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2440">
-        <v>1</v>
-      </c>
-      <c r="D2440">
-        <v>6067</v>
-      </c>
-      <c r="E2440">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2441" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2441">
-        <v>122</v>
-      </c>
-      <c r="B2441" s="10">
-        <v>46044</v>
-      </c>
-      <c r="C2441">
-        <v>1</v>
-      </c>
-      <c r="D2441">
-        <v>5960</v>
-      </c>
-      <c r="E2441">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2442" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2442">
-        <v>123</v>
-      </c>
-      <c r="B2442" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2442">
-        <v>0</v>
-      </c>
-      <c r="D2442">
-        <v>8800</v>
-      </c>
-      <c r="E2442">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2443" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2443">
-        <v>123</v>
-      </c>
-      <c r="B2443" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2443">
-        <v>0</v>
-      </c>
-      <c r="D2443">
-        <v>635</v>
-      </c>
-      <c r="E2443">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2444" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2444">
-        <v>123</v>
-      </c>
-      <c r="B2444" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2444">
-        <v>0</v>
-      </c>
-      <c r="D2444">
-        <v>9942</v>
-      </c>
-      <c r="E2444">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2445" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2445">
-        <v>123</v>
-      </c>
-      <c r="B2445" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2445">
-        <v>0</v>
-      </c>
-      <c r="D2445">
-        <v>5610</v>
-      </c>
-      <c r="E2445">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2446" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2446">
-        <v>123</v>
-      </c>
-      <c r="B2446" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2446">
-        <v>0</v>
-      </c>
-      <c r="D2446">
-        <v>259</v>
-      </c>
-      <c r="E2446">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2447" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2447">
-        <v>123</v>
-      </c>
-      <c r="B2447" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2447">
-        <v>0</v>
-      </c>
-      <c r="D2447">
-        <v>8798</v>
-      </c>
-      <c r="E2447">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2448" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2448">
-        <v>123</v>
-      </c>
-      <c r="B2448" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2448">
-        <v>0</v>
-      </c>
-      <c r="D2448">
-        <v>28</v>
-      </c>
-      <c r="E2448">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2449" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2449">
-        <v>123</v>
-      </c>
-      <c r="B2449" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2449">
-        <v>0</v>
-      </c>
-      <c r="D2449">
-        <v>1654</v>
-      </c>
-      <c r="E2449">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2450" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2450">
-        <v>123</v>
-      </c>
-      <c r="B2450" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2450">
-        <v>0</v>
-      </c>
-      <c r="D2450">
-        <v>1054</v>
-      </c>
-      <c r="E2450">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2451" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2451">
-        <v>123</v>
-      </c>
-      <c r="B2451" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2451">
-        <v>0</v>
-      </c>
-      <c r="D2451">
-        <v>8169</v>
-      </c>
-      <c r="E2451">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2452" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2452">
-        <v>123</v>
-      </c>
-      <c r="B2452" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2452">
-        <v>1</v>
-      </c>
-      <c r="D2452">
-        <v>5487</v>
-      </c>
-      <c r="E2452">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2453" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2453">
-        <v>123</v>
-      </c>
-      <c r="B2453" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2453">
-        <v>1</v>
-      </c>
-      <c r="D2453">
-        <v>922</v>
-      </c>
-      <c r="E2453">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2454" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2454">
-        <v>123</v>
-      </c>
-      <c r="B2454" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2454">
-        <v>1</v>
-      </c>
-      <c r="D2454">
-        <v>8568</v>
-      </c>
-      <c r="E2454">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2455" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2455">
-        <v>123</v>
-      </c>
-      <c r="B2455" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2455">
-        <v>1</v>
-      </c>
-      <c r="D2455">
-        <v>7254</v>
-      </c>
-      <c r="E2455">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2456" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2456">
-        <v>123</v>
-      </c>
-      <c r="B2456" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2456">
-        <v>1</v>
-      </c>
-      <c r="D2456">
-        <v>9479</v>
-      </c>
-      <c r="E2456">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2457" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2457">
-        <v>123</v>
-      </c>
-      <c r="B2457" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2457">
-        <v>1</v>
-      </c>
-      <c r="D2457">
-        <v>2233</v>
-      </c>
-      <c r="E2457">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2458" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2458">
-        <v>123</v>
-      </c>
-      <c r="B2458" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2458">
-        <v>1</v>
-      </c>
-      <c r="D2458">
-        <v>4070</v>
-      </c>
-      <c r="E2458">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2459" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2459">
-        <v>123</v>
-      </c>
-      <c r="B2459" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2459">
-        <v>1</v>
-      </c>
-      <c r="D2459">
-        <v>174</v>
-      </c>
-      <c r="E2459">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2460" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2460">
-        <v>123</v>
-      </c>
-      <c r="B2460" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2460">
-        <v>1</v>
-      </c>
-      <c r="D2460">
-        <v>896</v>
-      </c>
-      <c r="E2460">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2461" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2461">
-        <v>123</v>
-      </c>
-      <c r="B2461" s="10">
-        <v>46045</v>
-      </c>
-      <c r="C2461">
-        <v>1</v>
-      </c>
-      <c r="D2461">
-        <v>8470</v>
-      </c>
-      <c r="E2461">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2462" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2462">
-        <v>124</v>
-      </c>
-      <c r="B2462" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2462">
-        <v>0</v>
-      </c>
-      <c r="D2462">
-        <v>619</v>
-      </c>
-      <c r="E2462">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2463" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2463">
-        <v>124</v>
-      </c>
-      <c r="B2463" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2463">
-        <v>0</v>
-      </c>
-      <c r="D2463">
-        <v>9005</v>
-      </c>
-      <c r="E2463">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2464" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2464">
-        <v>124</v>
-      </c>
-      <c r="B2464" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2464">
-        <v>0</v>
-      </c>
-      <c r="D2464">
-        <v>3735</v>
-      </c>
-      <c r="E2464">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2465" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2465">
-        <v>124</v>
-      </c>
-      <c r="B2465" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2465">
-        <v>0</v>
-      </c>
-      <c r="D2465">
-        <v>828</v>
-      </c>
-      <c r="E2465">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2466" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2466">
-        <v>124</v>
-      </c>
-      <c r="B2466" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2466">
-        <v>0</v>
-      </c>
-      <c r="D2466">
-        <v>6042</v>
-      </c>
-      <c r="E2466">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2467" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2467">
-        <v>124</v>
-      </c>
-      <c r="B2467" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2467">
-        <v>0</v>
-      </c>
-      <c r="D2467">
-        <v>5067</v>
-      </c>
-      <c r="E2467">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2468" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2468">
-        <v>124</v>
-      </c>
-      <c r="B2468" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2468">
-        <v>0</v>
-      </c>
-      <c r="D2468">
-        <v>2078</v>
-      </c>
-      <c r="E2468">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2469" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2469">
-        <v>124</v>
-      </c>
-      <c r="B2469" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2469">
-        <v>0</v>
-      </c>
-      <c r="D2469">
-        <v>843</v>
-      </c>
-      <c r="E2469">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2470" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2470">
-        <v>124</v>
-      </c>
-      <c r="B2470" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2470">
-        <v>0</v>
-      </c>
-      <c r="D2470">
-        <v>3019</v>
-      </c>
-      <c r="E2470">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2471" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2471">
-        <v>124</v>
-      </c>
-      <c r="B2471" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2471">
-        <v>0</v>
-      </c>
-      <c r="D2471">
-        <v>3973</v>
-      </c>
-      <c r="E2471">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2472" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2472">
-        <v>124</v>
-      </c>
-      <c r="B2472" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2472">
-        <v>1</v>
-      </c>
-      <c r="D2472">
-        <v>3122</v>
-      </c>
-      <c r="E2472">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2473" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2473">
-        <v>124</v>
-      </c>
-      <c r="B2473" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2473">
-        <v>1</v>
-      </c>
-      <c r="D2473">
-        <v>2115</v>
-      </c>
-      <c r="E2473">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2474" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2474">
-        <v>124</v>
-      </c>
-      <c r="B2474" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2474">
-        <v>1</v>
-      </c>
-      <c r="D2474">
-        <v>1765</v>
-      </c>
-      <c r="E2474">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2475" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2475">
-        <v>124</v>
-      </c>
-      <c r="B2475" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2475">
-        <v>1</v>
-      </c>
-      <c r="D2475">
-        <v>4479</v>
-      </c>
-      <c r="E2475">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2476" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2476">
-        <v>124</v>
-      </c>
-      <c r="B2476" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2476">
-        <v>1</v>
-      </c>
-      <c r="D2476">
-        <v>8512</v>
-      </c>
-      <c r="E2476">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2477" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2477">
-        <v>124</v>
-      </c>
-      <c r="B2477" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2477">
-        <v>1</v>
-      </c>
-      <c r="D2477">
-        <v>4100</v>
-      </c>
-      <c r="E2477">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2478" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2478">
-        <v>124</v>
-      </c>
-      <c r="B2478" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2478">
-        <v>1</v>
-      </c>
-      <c r="D2478">
-        <v>5088</v>
-      </c>
-      <c r="E2478">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2479" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2479">
-        <v>124</v>
-      </c>
-      <c r="B2479" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2479">
-        <v>1</v>
-      </c>
-      <c r="D2479">
-        <v>8503</v>
-      </c>
-      <c r="E2479">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2480" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2480">
-        <v>124</v>
-      </c>
-      <c r="B2480" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2480">
-        <v>1</v>
-      </c>
-      <c r="D2480">
-        <v>243</v>
-      </c>
-      <c r="E2480">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2481" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2481">
-        <v>124</v>
-      </c>
-      <c r="B2481" s="10">
-        <v>46046</v>
-      </c>
-      <c r="C2481">
-        <v>1</v>
-      </c>
-      <c r="D2481">
-        <v>377</v>
-      </c>
-      <c r="E2481">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2482" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2482">
-        <v>125</v>
-      </c>
-      <c r="B2482" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2482">
-        <v>0</v>
-      </c>
-      <c r="D2482">
-        <v>2053</v>
-      </c>
-      <c r="E2482">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2483" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2483">
-        <v>125</v>
-      </c>
-      <c r="B2483" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2483">
-        <v>0</v>
-      </c>
-      <c r="D2483">
-        <v>1817</v>
-      </c>
-      <c r="E2483">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2484" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2484">
-        <v>125</v>
-      </c>
-      <c r="B2484" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2484">
-        <v>0</v>
-      </c>
-      <c r="D2484">
-        <v>1981</v>
-      </c>
-      <c r="E2484">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2485" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2485">
-        <v>125</v>
-      </c>
-      <c r="B2485" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2485">
-        <v>0</v>
-      </c>
-      <c r="D2485">
-        <v>5094</v>
-      </c>
-      <c r="E2485">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2486" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2486">
-        <v>125</v>
-      </c>
-      <c r="B2486" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2486">
-        <v>0</v>
-      </c>
-      <c r="D2486">
-        <v>8106</v>
-      </c>
-      <c r="E2486">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2487" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2487">
-        <v>125</v>
-      </c>
-      <c r="B2487" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2487">
-        <v>0</v>
-      </c>
-      <c r="D2487">
-        <v>3184</v>
-      </c>
-      <c r="E2487">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2488" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2488">
-        <v>125</v>
-      </c>
-      <c r="B2488" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2488">
-        <v>0</v>
-      </c>
-      <c r="D2488">
-        <v>1533</v>
-      </c>
-      <c r="E2488">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2489" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2489">
-        <v>125</v>
-      </c>
-      <c r="B2489" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2489">
-        <v>0</v>
-      </c>
-      <c r="D2489">
-        <v>1143</v>
-      </c>
-      <c r="E2489">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2490" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2490">
-        <v>125</v>
-      </c>
-      <c r="B2490" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2490">
-        <v>0</v>
-      </c>
-      <c r="D2490">
-        <v>9496</v>
-      </c>
-      <c r="E2490">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2491" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2491">
-        <v>125</v>
-      </c>
-      <c r="B2491" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2491">
-        <v>0</v>
-      </c>
-      <c r="D2491">
-        <v>4005</v>
-      </c>
-      <c r="E2491">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2492" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2492">
-        <v>125</v>
-      </c>
-      <c r="B2492" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2492">
-        <v>1</v>
-      </c>
-      <c r="D2492">
-        <v>2477</v>
-      </c>
-      <c r="E2492">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2493" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2493">
-        <v>125</v>
-      </c>
-      <c r="B2493" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2493">
-        <v>1</v>
-      </c>
-      <c r="D2493">
-        <v>6270</v>
-      </c>
-      <c r="E2493">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2494" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2494">
-        <v>125</v>
-      </c>
-      <c r="B2494" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2494">
-        <v>1</v>
-      </c>
-      <c r="D2494">
-        <v>3943</v>
-      </c>
-      <c r="E2494">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2495" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2495">
-        <v>125</v>
-      </c>
-      <c r="B2495" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2495">
-        <v>1</v>
-      </c>
-      <c r="D2495">
-        <v>7958</v>
-      </c>
-      <c r="E2495">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2496" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2496">
-        <v>125</v>
-      </c>
-      <c r="B2496" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2496">
-        <v>1</v>
-      </c>
-      <c r="D2496">
-        <v>4909</v>
-      </c>
-      <c r="E2496">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2497" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2497">
-        <v>125</v>
-      </c>
-      <c r="B2497" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2497">
-        <v>1</v>
-      </c>
-      <c r="D2497">
-        <v>9370</v>
-      </c>
-      <c r="E2497">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2498" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2498">
-        <v>125</v>
-      </c>
-      <c r="B2498" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2498">
-        <v>1</v>
-      </c>
-      <c r="D2498">
-        <v>2330</v>
-      </c>
-      <c r="E2498">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2499" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2499">
-        <v>125</v>
-      </c>
-      <c r="B2499" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2499">
-        <v>1</v>
-      </c>
-      <c r="D2499">
-        <v>7003</v>
-      </c>
-      <c r="E2499">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2500" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2500">
-        <v>125</v>
-      </c>
-      <c r="B2500" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2500">
-        <v>1</v>
-      </c>
-      <c r="D2500">
-        <v>9197</v>
-      </c>
-      <c r="E2500">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2501" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2501">
-        <v>125</v>
-      </c>
-      <c r="B2501" s="10">
-        <v>46048</v>
-      </c>
-      <c r="C2501">
-        <v>1</v>
-      </c>
-      <c r="D2501">
-        <v>1284</v>
-      </c>
-      <c r="E2501">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2502" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2502">
-        <v>126</v>
-      </c>
-      <c r="B2502" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2502">
-        <v>0</v>
-      </c>
-      <c r="D2502">
-        <v>6370</v>
-      </c>
-      <c r="E2502">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2503" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2503">
-        <v>126</v>
-      </c>
-      <c r="B2503" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2503">
-        <v>0</v>
-      </c>
-      <c r="D2503">
-        <v>1682</v>
-      </c>
-      <c r="E2503">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2504" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2504">
-        <v>126</v>
-      </c>
-      <c r="B2504" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2504">
-        <v>0</v>
-      </c>
-      <c r="D2504">
-        <v>1618</v>
-      </c>
-      <c r="E2504">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2505" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2505">
-        <v>126</v>
-      </c>
-      <c r="B2505" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2505">
-        <v>0</v>
-      </c>
-      <c r="D2505">
-        <v>5890</v>
-      </c>
-      <c r="E2505">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2506" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2506">
-        <v>126</v>
-      </c>
-      <c r="B2506" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2506">
-        <v>0</v>
-      </c>
-      <c r="D2506">
-        <v>3548</v>
-      </c>
-      <c r="E2506">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2507" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2507">
-        <v>126</v>
-      </c>
-      <c r="B2507" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2507">
-        <v>0</v>
-      </c>
-      <c r="D2507">
-        <v>8031</v>
-      </c>
-      <c r="E2507">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2508" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2508">
-        <v>126</v>
-      </c>
-      <c r="B2508" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2508">
-        <v>0</v>
-      </c>
-      <c r="D2508">
-        <v>2391</v>
-      </c>
-      <c r="E2508">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2509" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2509">
-        <v>126</v>
-      </c>
-      <c r="B2509" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2509">
-        <v>0</v>
-      </c>
-      <c r="D2509">
-        <v>8811</v>
-      </c>
-      <c r="E2509">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2510" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2510">
-        <v>126</v>
-      </c>
-      <c r="B2510" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2510">
-        <v>0</v>
-      </c>
-      <c r="D2510">
-        <v>8762</v>
-      </c>
-      <c r="E2510">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2511" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2511">
-        <v>126</v>
-      </c>
-      <c r="B2511" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2511">
-        <v>1</v>
-      </c>
-      <c r="D2511">
-        <v>1326</v>
-      </c>
-      <c r="E2511">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2512" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2512">
-        <v>126</v>
-      </c>
-      <c r="B2512" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2512">
-        <v>1</v>
-      </c>
-      <c r="D2512">
-        <v>8815</v>
-      </c>
-      <c r="E2512">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2513" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2513">
-        <v>126</v>
-      </c>
-      <c r="B2513" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2513">
-        <v>1</v>
-      </c>
-      <c r="D2513">
-        <v>1114</v>
-      </c>
-      <c r="E2513">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2514" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2514">
-        <v>126</v>
-      </c>
-      <c r="B2514" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2514">
-        <v>1</v>
-      </c>
-      <c r="D2514">
-        <v>9377</v>
-      </c>
-      <c r="E2514">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2515" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2515">
-        <v>126</v>
-      </c>
-      <c r="B2515" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2515">
-        <v>1</v>
-      </c>
-      <c r="D2515">
-        <v>228</v>
-      </c>
-      <c r="E2515">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2516" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2516">
-        <v>126</v>
-      </c>
-      <c r="B2516" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2516">
-        <v>1</v>
-      </c>
-      <c r="D2516">
-        <v>5561</v>
-      </c>
-      <c r="E2516">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2517" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2517">
-        <v>126</v>
-      </c>
-      <c r="B2517" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2517">
-        <v>1</v>
-      </c>
-      <c r="D2517">
-        <v>9191</v>
-      </c>
-      <c r="E2517">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2518" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2518">
-        <v>126</v>
-      </c>
-      <c r="B2518" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2518">
-        <v>1</v>
-      </c>
-      <c r="D2518">
-        <v>7949</v>
-      </c>
-      <c r="E2518">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2519" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2519">
-        <v>126</v>
-      </c>
-      <c r="B2519" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2519">
-        <v>1</v>
-      </c>
-      <c r="D2519">
-        <v>7972</v>
-      </c>
-      <c r="E2519">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2520" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2520">
-        <v>126</v>
-      </c>
-      <c r="B2520" s="10">
-        <v>46049</v>
-      </c>
-      <c r="C2520">
-        <v>1</v>
-      </c>
-      <c r="D2520">
-        <v>7263</v>
-      </c>
-      <c r="E2520">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2521" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2521">
-        <v>127</v>
-      </c>
-      <c r="B2521" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2521">
-        <v>0</v>
-      </c>
-      <c r="D2521">
-        <v>7384</v>
-      </c>
-      <c r="E2521">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2522" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2522">
-        <v>127</v>
-      </c>
-      <c r="B2522" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2522">
-        <v>0</v>
-      </c>
-      <c r="D2522">
-        <v>1595</v>
-      </c>
-      <c r="E2522">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2523" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2523">
-        <v>127</v>
-      </c>
-      <c r="B2523" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2523">
-        <v>0</v>
-      </c>
-      <c r="D2523">
-        <v>1221</v>
-      </c>
-      <c r="E2523">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2524" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2524">
-        <v>127</v>
-      </c>
-      <c r="B2524" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2524">
-        <v>0</v>
-      </c>
-      <c r="D2524">
-        <v>9896</v>
-      </c>
-      <c r="E2524">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2525" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2525">
-        <v>127</v>
-      </c>
-      <c r="B2525" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2525">
-        <v>0</v>
-      </c>
-      <c r="D2525">
-        <v>2902</v>
-      </c>
-      <c r="E2525">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2526" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2526">
-        <v>127</v>
-      </c>
-      <c r="B2526" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2526">
-        <v>0</v>
-      </c>
-      <c r="D2526">
-        <v>1602</v>
-      </c>
-      <c r="E2526">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2527" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2527">
-        <v>127</v>
-      </c>
-      <c r="B2527" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2527">
-        <v>0</v>
-      </c>
-      <c r="D2527">
-        <v>4286</v>
-      </c>
-      <c r="E2527">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2528" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2528">
-        <v>127</v>
-      </c>
-      <c r="B2528" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2528">
-        <v>0</v>
-      </c>
-      <c r="D2528">
-        <v>6772</v>
-      </c>
-      <c r="E2528">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2529" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2529">
-        <v>127</v>
-      </c>
-      <c r="B2529" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2529">
-        <v>0</v>
-      </c>
-      <c r="D2529">
-        <v>6380</v>
-      </c>
-      <c r="E2529">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2530" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2530">
-        <v>127</v>
-      </c>
-      <c r="B2530" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2530">
-        <v>0</v>
-      </c>
-      <c r="D2530">
-        <v>9380</v>
-      </c>
-      <c r="E2530">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2531" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2531">
-        <v>127</v>
-      </c>
-      <c r="B2531" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2531">
-        <v>1</v>
-      </c>
-      <c r="D2531">
-        <v>9043</v>
-      </c>
-      <c r="E2531">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2532" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2532">
-        <v>127</v>
-      </c>
-      <c r="B2532" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2532">
-        <v>1</v>
-      </c>
-      <c r="D2532">
-        <v>4709</v>
-      </c>
-      <c r="E2532">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2533" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2533">
-        <v>127</v>
-      </c>
-      <c r="B2533" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2533">
-        <v>1</v>
-      </c>
-      <c r="D2533">
-        <v>9631</v>
-      </c>
-      <c r="E2533">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2534" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2534">
-        <v>127</v>
-      </c>
-      <c r="B2534" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2534">
-        <v>1</v>
-      </c>
-      <c r="D2534">
-        <v>1758</v>
-      </c>
-      <c r="E2534">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2535" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2535">
-        <v>127</v>
-      </c>
-      <c r="B2535" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2535">
-        <v>1</v>
-      </c>
-      <c r="D2535">
-        <v>7218</v>
-      </c>
-      <c r="E2535">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2536" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2536">
-        <v>127</v>
-      </c>
-      <c r="B2536" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2536">
-        <v>1</v>
-      </c>
-      <c r="D2536">
-        <v>2620</v>
-      </c>
-      <c r="E2536">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2537" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2537">
-        <v>127</v>
-      </c>
-      <c r="B2537" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2537">
-        <v>1</v>
-      </c>
-      <c r="D2537">
-        <v>2966</v>
-      </c>
-      <c r="E2537">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2538" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2538">
-        <v>127</v>
-      </c>
-      <c r="B2538" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2538">
-        <v>1</v>
-      </c>
-      <c r="D2538">
-        <v>2611</v>
-      </c>
-      <c r="E2538">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2539" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2539">
-        <v>127</v>
-      </c>
-      <c r="B2539" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2539">
-        <v>1</v>
-      </c>
-      <c r="D2539">
-        <v>5596</v>
-      </c>
-      <c r="E2539">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2540" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2540">
-        <v>127</v>
-      </c>
-      <c r="B2540" s="10">
-        <v>46050</v>
-      </c>
-      <c r="C2540">
-        <v>1</v>
-      </c>
-      <c r="D2540">
-        <v>3092</v>
-      </c>
-      <c r="E2540">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2541" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2541">
-        <v>128</v>
-      </c>
-      <c r="B2541" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2541">
-        <v>0</v>
-      </c>
-      <c r="D2541">
-        <v>6346</v>
-      </c>
-      <c r="E2541">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2542" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2542">
-        <v>128</v>
-      </c>
-      <c r="B2542" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2542">
-        <v>0</v>
-      </c>
-      <c r="D2542">
-        <v>9722</v>
-      </c>
-      <c r="E2542">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2543" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2543">
-        <v>128</v>
-      </c>
-      <c r="B2543" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2543">
-        <v>0</v>
-      </c>
-      <c r="D2543">
-        <v>6666</v>
-      </c>
-      <c r="E2543">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2544" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2544">
-        <v>128</v>
-      </c>
-      <c r="B2544" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2544">
-        <v>0</v>
-      </c>
-      <c r="D2544">
-        <v>8204</v>
-      </c>
-      <c r="E2544">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2545" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2545">
-        <v>128</v>
-      </c>
-      <c r="B2545" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2545">
-        <v>0</v>
-      </c>
-      <c r="D2545">
-        <v>9273</v>
-      </c>
-      <c r="E2545">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2546" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2546">
-        <v>128</v>
-      </c>
-      <c r="B2546" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2546">
-        <v>0</v>
-      </c>
-      <c r="D2546">
-        <v>65</v>
-      </c>
-      <c r="E2546">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2547" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2547">
-        <v>128</v>
-      </c>
-      <c r="B2547" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2547">
-        <v>0</v>
-      </c>
-      <c r="D2547">
-        <v>6085</v>
-      </c>
-      <c r="E2547">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2548" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2548">
-        <v>128</v>
-      </c>
-      <c r="B2548" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2548">
-        <v>0</v>
-      </c>
-      <c r="D2548">
-        <v>8956</v>
-      </c>
-      <c r="E2548">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2549" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2549">
-        <v>128</v>
-      </c>
-      <c r="B2549" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2549">
-        <v>0</v>
-      </c>
-      <c r="D2549">
-        <v>6712</v>
-      </c>
-      <c r="E2549">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2550" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2550">
-        <v>128</v>
-      </c>
-      <c r="B2550" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2550">
-        <v>0</v>
-      </c>
-      <c r="D2550">
-        <v>2478</v>
-      </c>
-      <c r="E2550">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2551" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2551">
-        <v>128</v>
-      </c>
-      <c r="B2551" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2551">
-        <v>1</v>
-      </c>
-      <c r="D2551">
-        <v>9753</v>
-      </c>
-      <c r="E2551">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2552" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2552">
-        <v>128</v>
-      </c>
-      <c r="B2552" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2552">
-        <v>1</v>
-      </c>
-      <c r="D2552">
-        <v>4687</v>
-      </c>
-      <c r="E2552">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2553" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2553">
-        <v>128</v>
-      </c>
-      <c r="B2553" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2553">
-        <v>1</v>
-      </c>
-      <c r="D2553">
-        <v>9515</v>
-      </c>
-      <c r="E2553">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2554" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2554">
-        <v>128</v>
-      </c>
-      <c r="B2554" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2554">
-        <v>1</v>
-      </c>
-      <c r="D2554">
-        <v>5996</v>
-      </c>
-      <c r="E2554">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2555" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2555">
-        <v>128</v>
-      </c>
-      <c r="B2555" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2555">
-        <v>1</v>
-      </c>
-      <c r="D2555">
-        <v>6303</v>
-      </c>
-      <c r="E2555">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2556" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2556">
-        <v>128</v>
-      </c>
-      <c r="B2556" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2556">
-        <v>1</v>
-      </c>
-      <c r="D2556">
-        <v>9258</v>
-      </c>
-      <c r="E2556">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2557" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2557">
-        <v>128</v>
-      </c>
-      <c r="B2557" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2557">
-        <v>1</v>
-      </c>
-      <c r="D2557">
-        <v>436</v>
-      </c>
-      <c r="E2557">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2558" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2558">
-        <v>128</v>
-      </c>
-      <c r="B2558" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2558">
-        <v>1</v>
-      </c>
-      <c r="D2558">
-        <v>620</v>
-      </c>
-      <c r="E2558">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2559" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2559">
-        <v>128</v>
-      </c>
-      <c r="B2559" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2559">
-        <v>1</v>
-      </c>
-      <c r="D2559">
-        <v>9008</v>
-      </c>
-      <c r="E2559">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2560" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2560">
-        <v>128</v>
-      </c>
-      <c r="B2560" s="10">
-        <v>46051</v>
-      </c>
-      <c r="C2560">
-        <v>1</v>
-      </c>
-      <c r="D2560">
-        <v>7080</v>
-      </c>
-      <c r="E2560">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2561" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2561">
-        <v>129</v>
-      </c>
-      <c r="B2561" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2561">
-        <v>0</v>
-      </c>
-      <c r="D2561">
-        <v>9172</v>
-      </c>
-      <c r="E2561">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2562" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2562">
-        <v>129</v>
-      </c>
-      <c r="B2562" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2562">
-        <v>0</v>
-      </c>
-      <c r="D2562">
-        <v>1368</v>
-      </c>
-      <c r="E2562">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2563" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2563">
-        <v>129</v>
-      </c>
-      <c r="B2563" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2563">
-        <v>0</v>
-      </c>
-      <c r="D2563">
-        <v>7720</v>
-      </c>
-      <c r="E2563">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2564" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2564">
-        <v>129</v>
-      </c>
-      <c r="B2564" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2564">
-        <v>0</v>
-      </c>
-      <c r="D2564">
-        <v>1622</v>
-      </c>
-      <c r="E2564">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2565" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2565">
-        <v>129</v>
-      </c>
-      <c r="B2565" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2565">
-        <v>0</v>
-      </c>
-      <c r="D2565">
-        <v>8306</v>
-      </c>
-      <c r="E2565">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2566" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2566">
-        <v>129</v>
-      </c>
-      <c r="B2566" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2566">
-        <v>0</v>
-      </c>
-      <c r="D2566">
-        <v>2227</v>
-      </c>
-      <c r="E2566">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2567" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2567">
-        <v>129</v>
-      </c>
-      <c r="B2567" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2567">
-        <v>0</v>
-      </c>
-      <c r="D2567">
-        <v>9527</v>
-      </c>
-      <c r="E2567">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2568" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2568">
-        <v>129</v>
-      </c>
-      <c r="B2568" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2568">
-        <v>0</v>
-      </c>
-      <c r="D2568">
-        <v>6534</v>
-      </c>
-      <c r="E2568">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2569" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2569">
-        <v>129</v>
-      </c>
-      <c r="B2569" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2569">
-        <v>0</v>
-      </c>
-      <c r="D2569">
-        <v>7564</v>
-      </c>
-      <c r="E2569">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2570" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2570">
-        <v>129</v>
-      </c>
-      <c r="B2570" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2570">
-        <v>0</v>
-      </c>
-      <c r="D2570">
-        <v>4182</v>
-      </c>
-      <c r="E2570">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2571" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2571">
-        <v>129</v>
-      </c>
-      <c r="B2571" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2571">
-        <v>1</v>
-      </c>
-      <c r="D2571">
-        <v>3248</v>
-      </c>
-      <c r="E2571">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2572" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2572">
-        <v>129</v>
-      </c>
-      <c r="B2572" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2572">
-        <v>1</v>
-      </c>
-      <c r="D2572">
-        <v>211</v>
-      </c>
-      <c r="E2572">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2573" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2573">
-        <v>129</v>
-      </c>
-      <c r="B2573" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2573">
-        <v>1</v>
-      </c>
-      <c r="D2573">
-        <v>1817</v>
-      </c>
-      <c r="E2573">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2574" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2574">
-        <v>129</v>
-      </c>
-      <c r="B2574" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2574">
-        <v>1</v>
-      </c>
-      <c r="D2574">
-        <v>244</v>
-      </c>
-      <c r="E2574">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2575" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2575">
-        <v>129</v>
-      </c>
-      <c r="B2575" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2575">
-        <v>1</v>
-      </c>
-      <c r="D2575">
-        <v>8190</v>
-      </c>
-      <c r="E2575">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2576" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2576">
-        <v>129</v>
-      </c>
-      <c r="B2576" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2576">
-        <v>1</v>
-      </c>
-      <c r="D2576">
-        <v>1360</v>
-      </c>
-      <c r="E2576">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2577" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2577">
-        <v>129</v>
-      </c>
-      <c r="B2577" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2577">
-        <v>1</v>
-      </c>
-      <c r="D2577">
-        <v>4335</v>
-      </c>
-      <c r="E2577">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2578" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2578">
-        <v>129</v>
-      </c>
-      <c r="B2578" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2578">
-        <v>1</v>
-      </c>
-      <c r="D2578">
-        <v>7017</v>
-      </c>
-      <c r="E2578">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2579" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2579">
-        <v>129</v>
-      </c>
-      <c r="B2579" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2579">
-        <v>1</v>
-      </c>
-      <c r="D2579">
-        <v>1445</v>
-      </c>
-      <c r="E2579">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2580" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2580">
-        <v>129</v>
-      </c>
-      <c r="B2580" s="10">
-        <v>46052</v>
-      </c>
-      <c r="C2580">
-        <v>1</v>
-      </c>
-      <c r="D2580">
-        <v>1476</v>
-      </c>
-      <c r="E2580">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2581" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2581">
-        <v>130</v>
-      </c>
-      <c r="B2581" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2581">
-        <v>0</v>
-      </c>
-      <c r="D2581">
-        <v>2457</v>
-      </c>
-      <c r="E2581">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2582" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2582">
-        <v>130</v>
-      </c>
-      <c r="B2582" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2582">
-        <v>0</v>
-      </c>
-      <c r="D2582">
-        <v>6296</v>
-      </c>
-      <c r="E2582">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2583" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2583">
-        <v>130</v>
-      </c>
-      <c r="B2583" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2583">
-        <v>0</v>
-      </c>
-      <c r="D2583">
-        <v>7873</v>
-      </c>
-      <c r="E2583">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2584" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2584">
-        <v>130</v>
-      </c>
-      <c r="B2584" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2584">
-        <v>0</v>
-      </c>
-      <c r="D2584">
-        <v>4926</v>
-      </c>
-      <c r="E2584">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2585" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2585">
-        <v>130</v>
-      </c>
-      <c r="B2585" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2585">
-        <v>0</v>
-      </c>
-      <c r="D2585">
-        <v>3125</v>
-      </c>
-      <c r="E2585">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2586" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2586">
-        <v>130</v>
-      </c>
-      <c r="B2586" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2586">
-        <v>0</v>
-      </c>
-      <c r="D2586">
-        <v>9687</v>
-      </c>
-      <c r="E2586">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2587" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2587">
-        <v>130</v>
-      </c>
-      <c r="B2587" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2587">
-        <v>0</v>
-      </c>
-      <c r="D2587">
-        <v>2379</v>
-      </c>
-      <c r="E2587">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2588" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2588">
-        <v>130</v>
-      </c>
-      <c r="B2588" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2588">
-        <v>0</v>
-      </c>
-      <c r="D2588">
-        <v>8508</v>
-      </c>
-      <c r="E2588">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2589" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2589">
-        <v>130</v>
-      </c>
-      <c r="B2589" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2589">
-        <v>0</v>
-      </c>
-      <c r="D2589">
-        <v>6188</v>
-      </c>
-      <c r="E2589">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2590" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2590">
-        <v>130</v>
-      </c>
-      <c r="B2590" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2590">
-        <v>0</v>
-      </c>
-      <c r="D2590">
-        <v>1888</v>
-      </c>
-      <c r="E2590">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2591" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2591">
-        <v>130</v>
-      </c>
-      <c r="B2591" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2591">
-        <v>1</v>
-      </c>
-      <c r="D2591">
-        <v>295</v>
-      </c>
-      <c r="E2591">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2592" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2592">
-        <v>130</v>
-      </c>
-      <c r="B2592" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2592">
-        <v>1</v>
-      </c>
-      <c r="D2592">
-        <v>6984</v>
-      </c>
-      <c r="E2592">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2593" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2593">
-        <v>130</v>
-      </c>
-      <c r="B2593" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2593">
-        <v>1</v>
-      </c>
-      <c r="D2593">
-        <v>8710</v>
-      </c>
-      <c r="E2593">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2594" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2594">
-        <v>130</v>
-      </c>
-      <c r="B2594" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2594">
-        <v>1</v>
-      </c>
-      <c r="D2594">
-        <v>870</v>
-      </c>
-      <c r="E2594">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2595" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2595">
-        <v>130</v>
-      </c>
-      <c r="B2595" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2595">
-        <v>1</v>
-      </c>
-      <c r="D2595">
-        <v>8206</v>
-      </c>
-      <c r="E2595">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2596" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2596">
-        <v>130</v>
-      </c>
-      <c r="B2596" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2596">
-        <v>1</v>
-      </c>
-      <c r="D2596">
-        <v>1928</v>
-      </c>
-      <c r="E2596">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2597" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2597">
-        <v>130</v>
-      </c>
-      <c r="B2597" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2597">
-        <v>1</v>
-      </c>
-      <c r="D2597">
-        <v>8451</v>
-      </c>
-      <c r="E2597">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2598" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2598">
-        <v>130</v>
-      </c>
-      <c r="B2598" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2598">
-        <v>1</v>
-      </c>
-      <c r="D2598">
-        <v>6326</v>
-      </c>
-      <c r="E2598">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2599" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2599">
-        <v>130</v>
-      </c>
-      <c r="B2599" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2599">
-        <v>1</v>
-      </c>
-      <c r="D2599">
-        <v>4344</v>
-      </c>
-      <c r="E2599">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2600" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2600">
-        <v>130</v>
-      </c>
-      <c r="B2600" s="10">
-        <v>46053</v>
-      </c>
-      <c r="C2600">
-        <v>1</v>
-      </c>
-      <c r="D2600">
-        <v>3515</v>
-      </c>
-      <c r="E2600">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/primeirasemanasetembro.xlsx
+++ b/primeirasemanasetembro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivina\Desktop\jogodobicho\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3AB105-B635-40A8-B19E-9E86176782EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF09CE6E-EF77-4F5F-BFC2-9D1B9D3B3378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{500AFD6E-13E7-4543-8FDB-D63E104D29D0}"/>
   </bookViews>
@@ -539,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6185FBA4-3391-45B3-811A-4861B6CE3709}">
-  <dimension ref="A1:T2321"/>
+  <dimension ref="A1:T2381"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.44140625" customWidth="1"/>
@@ -40798,6 +40798,1026 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2322" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2322">
+        <v>117</v>
+      </c>
+      <c r="B2322" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2322">
+        <v>0</v>
+      </c>
+      <c r="D2322">
+        <v>2053</v>
+      </c>
+      <c r="E2322">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2323">
+        <v>117</v>
+      </c>
+      <c r="B2323" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2323">
+        <v>0</v>
+      </c>
+      <c r="D2323">
+        <v>1817</v>
+      </c>
+      <c r="E2323">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2324">
+        <v>117</v>
+      </c>
+      <c r="B2324" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2324">
+        <v>0</v>
+      </c>
+      <c r="D2324">
+        <v>1981</v>
+      </c>
+      <c r="E2324">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2325">
+        <v>117</v>
+      </c>
+      <c r="B2325" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2325">
+        <v>0</v>
+      </c>
+      <c r="D2325">
+        <v>5094</v>
+      </c>
+      <c r="E2325">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2326">
+        <v>117</v>
+      </c>
+      <c r="B2326" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2326">
+        <v>0</v>
+      </c>
+      <c r="D2326">
+        <v>8106</v>
+      </c>
+      <c r="E2326">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2327">
+        <v>117</v>
+      </c>
+      <c r="B2327" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2327">
+        <v>0</v>
+      </c>
+      <c r="D2327">
+        <v>3184</v>
+      </c>
+      <c r="E2327">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2328">
+        <v>117</v>
+      </c>
+      <c r="B2328" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2328">
+        <v>0</v>
+      </c>
+      <c r="D2328">
+        <v>1533</v>
+      </c>
+      <c r="E2328">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2329">
+        <v>117</v>
+      </c>
+      <c r="B2329" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2329">
+        <v>0</v>
+      </c>
+      <c r="D2329">
+        <v>1143</v>
+      </c>
+      <c r="E2329">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2330">
+        <v>117</v>
+      </c>
+      <c r="B2330" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2330">
+        <v>0</v>
+      </c>
+      <c r="D2330">
+        <v>9496</v>
+      </c>
+      <c r="E2330">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2331">
+        <v>117</v>
+      </c>
+      <c r="B2331" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2331">
+        <v>0</v>
+      </c>
+      <c r="D2331">
+        <v>4005</v>
+      </c>
+      <c r="E2331">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2332">
+        <v>117</v>
+      </c>
+      <c r="B2332" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2332">
+        <v>1</v>
+      </c>
+      <c r="D2332">
+        <v>2371</v>
+      </c>
+      <c r="E2332">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2333">
+        <v>117</v>
+      </c>
+      <c r="B2333" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2333">
+        <v>1</v>
+      </c>
+      <c r="D2333">
+        <v>4266</v>
+      </c>
+      <c r="E2333">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2334">
+        <v>117</v>
+      </c>
+      <c r="B2334" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2334">
+        <v>1</v>
+      </c>
+      <c r="D2334">
+        <v>9275</v>
+      </c>
+      <c r="E2334">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2335">
+        <v>117</v>
+      </c>
+      <c r="B2335" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2335">
+        <v>1</v>
+      </c>
+      <c r="D2335">
+        <v>6352</v>
+      </c>
+      <c r="E2335">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2336">
+        <v>117</v>
+      </c>
+      <c r="B2336" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2336">
+        <v>1</v>
+      </c>
+      <c r="D2336">
+        <v>4087</v>
+      </c>
+      <c r="E2336">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2337">
+        <v>117</v>
+      </c>
+      <c r="B2337" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2337">
+        <v>1</v>
+      </c>
+      <c r="D2337">
+        <v>6793</v>
+      </c>
+      <c r="E2337">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2338">
+        <v>117</v>
+      </c>
+      <c r="B2338" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2338">
+        <v>1</v>
+      </c>
+      <c r="D2338">
+        <v>8109</v>
+      </c>
+      <c r="E2338">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2339">
+        <v>117</v>
+      </c>
+      <c r="B2339" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2339">
+        <v>1</v>
+      </c>
+      <c r="D2339">
+        <v>101</v>
+      </c>
+      <c r="E2339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2340">
+        <v>117</v>
+      </c>
+      <c r="B2340" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2340">
+        <v>1</v>
+      </c>
+      <c r="D2340">
+        <v>6727</v>
+      </c>
+      <c r="E2340">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2341">
+        <v>117</v>
+      </c>
+      <c r="B2341" s="10">
+        <v>46038</v>
+      </c>
+      <c r="C2341">
+        <v>1</v>
+      </c>
+      <c r="D2341">
+        <v>9688</v>
+      </c>
+      <c r="E2341">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2342">
+        <v>118</v>
+      </c>
+      <c r="B2342" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2342">
+        <v>0</v>
+      </c>
+      <c r="D2342">
+        <v>4855</v>
+      </c>
+      <c r="E2342">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2343">
+        <v>118</v>
+      </c>
+      <c r="B2343" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2343">
+        <v>0</v>
+      </c>
+      <c r="D2343">
+        <v>7141</v>
+      </c>
+      <c r="E2343">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2344">
+        <v>118</v>
+      </c>
+      <c r="B2344" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2344">
+        <v>0</v>
+      </c>
+      <c r="D2344">
+        <v>4432</v>
+      </c>
+      <c r="E2344">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2345">
+        <v>118</v>
+      </c>
+      <c r="B2345" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2345">
+        <v>0</v>
+      </c>
+      <c r="D2345">
+        <v>2831</v>
+      </c>
+      <c r="E2345">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2346">
+        <v>118</v>
+      </c>
+      <c r="B2346" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2346">
+        <v>0</v>
+      </c>
+      <c r="D2346">
+        <v>1011</v>
+      </c>
+      <c r="E2346">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2347">
+        <v>118</v>
+      </c>
+      <c r="B2347" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2347">
+        <v>0</v>
+      </c>
+      <c r="D2347">
+        <v>4041</v>
+      </c>
+      <c r="E2347">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2348">
+        <v>118</v>
+      </c>
+      <c r="B2348" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2348">
+        <v>0</v>
+      </c>
+      <c r="D2348">
+        <v>6708</v>
+      </c>
+      <c r="E2348">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2349">
+        <v>118</v>
+      </c>
+      <c r="B2349" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2349">
+        <v>0</v>
+      </c>
+      <c r="D2349">
+        <v>8768</v>
+      </c>
+      <c r="E2349">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2350">
+        <v>118</v>
+      </c>
+      <c r="B2350" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2350">
+        <v>0</v>
+      </c>
+      <c r="D2350">
+        <v>336</v>
+      </c>
+      <c r="E2350">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2351">
+        <v>118</v>
+      </c>
+      <c r="B2351" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2351">
+        <v>0</v>
+      </c>
+      <c r="D2351">
+        <v>2819</v>
+      </c>
+      <c r="E2351">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2352">
+        <v>118</v>
+      </c>
+      <c r="B2352" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2352">
+        <v>1</v>
+      </c>
+      <c r="D2352">
+        <v>5354</v>
+      </c>
+      <c r="E2352">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2353">
+        <v>118</v>
+      </c>
+      <c r="B2353" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2353">
+        <v>1</v>
+      </c>
+      <c r="D2353">
+        <v>7161</v>
+      </c>
+      <c r="E2353">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2354">
+        <v>118</v>
+      </c>
+      <c r="B2354" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2354">
+        <v>1</v>
+      </c>
+      <c r="D2354">
+        <v>5777</v>
+      </c>
+      <c r="E2354">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2355">
+        <v>118</v>
+      </c>
+      <c r="B2355" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2355">
+        <v>1</v>
+      </c>
+      <c r="D2355">
+        <v>9215</v>
+      </c>
+      <c r="E2355">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2356">
+        <v>118</v>
+      </c>
+      <c r="B2356" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2356">
+        <v>1</v>
+      </c>
+      <c r="D2356">
+        <v>3145</v>
+      </c>
+      <c r="E2356">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2357">
+        <v>118</v>
+      </c>
+      <c r="B2357" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2357">
+        <v>1</v>
+      </c>
+      <c r="D2357">
+        <v>2537</v>
+      </c>
+      <c r="E2357">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2358">
+        <v>118</v>
+      </c>
+      <c r="B2358" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2358">
+        <v>1</v>
+      </c>
+      <c r="D2358">
+        <v>2349</v>
+      </c>
+      <c r="E2358">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2359">
+        <v>118</v>
+      </c>
+      <c r="B2359" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2359">
+        <v>1</v>
+      </c>
+      <c r="D2359">
+        <v>6278</v>
+      </c>
+      <c r="E2359">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2360">
+        <v>118</v>
+      </c>
+      <c r="B2360" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2360">
+        <v>1</v>
+      </c>
+      <c r="D2360">
+        <v>2937</v>
+      </c>
+      <c r="E2360">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2361">
+        <v>118</v>
+      </c>
+      <c r="B2361" s="10">
+        <v>46039</v>
+      </c>
+      <c r="C2361">
+        <v>1</v>
+      </c>
+      <c r="D2361">
+        <v>1334</v>
+      </c>
+      <c r="E2361">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2362">
+        <v>119</v>
+      </c>
+      <c r="B2362" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2362">
+        <v>0</v>
+      </c>
+      <c r="D2362">
+        <v>6418</v>
+      </c>
+      <c r="E2362">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2363">
+        <v>119</v>
+      </c>
+      <c r="B2363" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2363">
+        <v>0</v>
+      </c>
+      <c r="D2363">
+        <v>4211</v>
+      </c>
+      <c r="E2363">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2364">
+        <v>119</v>
+      </c>
+      <c r="B2364" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2364">
+        <v>0</v>
+      </c>
+      <c r="D2364">
+        <v>1811</v>
+      </c>
+      <c r="E2364">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2365">
+        <v>119</v>
+      </c>
+      <c r="B2365" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2365">
+        <v>0</v>
+      </c>
+      <c r="D2365">
+        <v>5563</v>
+      </c>
+      <c r="E2365">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2366">
+        <v>119</v>
+      </c>
+      <c r="B2366" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2366">
+        <v>0</v>
+      </c>
+      <c r="D2366">
+        <v>1821</v>
+      </c>
+      <c r="E2366">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2367">
+        <v>119</v>
+      </c>
+      <c r="B2367" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2367">
+        <v>0</v>
+      </c>
+      <c r="D2367">
+        <v>9057</v>
+      </c>
+      <c r="E2367">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2368">
+        <v>119</v>
+      </c>
+      <c r="B2368" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2368">
+        <v>0</v>
+      </c>
+      <c r="D2368">
+        <v>8181</v>
+      </c>
+      <c r="E2368">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2369">
+        <v>119</v>
+      </c>
+      <c r="B2369" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2369">
+        <v>0</v>
+      </c>
+      <c r="D2369">
+        <v>9671</v>
+      </c>
+      <c r="E2369">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2370">
+        <v>119</v>
+      </c>
+      <c r="B2370" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2370">
+        <v>0</v>
+      </c>
+      <c r="D2370">
+        <v>8850</v>
+      </c>
+      <c r="E2370">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2371">
+        <v>119</v>
+      </c>
+      <c r="B2371" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2371">
+        <v>0</v>
+      </c>
+      <c r="D2371">
+        <v>4769</v>
+      </c>
+      <c r="E2371">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2372">
+        <v>119</v>
+      </c>
+      <c r="B2372" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2372">
+        <v>1</v>
+      </c>
+      <c r="D2372">
+        <v>2915</v>
+      </c>
+      <c r="E2372">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2373">
+        <v>119</v>
+      </c>
+      <c r="B2373" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2373">
+        <v>1</v>
+      </c>
+      <c r="D2373">
+        <v>8569</v>
+      </c>
+      <c r="E2373">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2374">
+        <v>119</v>
+      </c>
+      <c r="B2374" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2374">
+        <v>1</v>
+      </c>
+      <c r="D2374">
+        <v>2222</v>
+      </c>
+      <c r="E2374">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2375">
+        <v>119</v>
+      </c>
+      <c r="B2375" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2375">
+        <v>1</v>
+      </c>
+      <c r="D2375">
+        <v>9331</v>
+      </c>
+      <c r="E2375">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2376">
+        <v>119</v>
+      </c>
+      <c r="B2376" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2376">
+        <v>1</v>
+      </c>
+      <c r="D2376">
+        <v>5980</v>
+      </c>
+      <c r="E2376">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2377">
+        <v>119</v>
+      </c>
+      <c r="B2377" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2377">
+        <v>1</v>
+      </c>
+      <c r="D2377">
+        <v>5306</v>
+      </c>
+      <c r="E2377">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2378">
+        <v>119</v>
+      </c>
+      <c r="B2378" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2378">
+        <v>1</v>
+      </c>
+      <c r="D2378">
+        <v>197</v>
+      </c>
+      <c r="E2378">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2379">
+        <v>119</v>
+      </c>
+      <c r="B2379" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2379">
+        <v>1</v>
+      </c>
+      <c r="D2379">
+        <v>1371</v>
+      </c>
+      <c r="E2379">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2380">
+        <v>119</v>
+      </c>
+      <c r="B2380" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2380">
+        <v>1</v>
+      </c>
+      <c r="D2380">
+        <v>358</v>
+      </c>
+      <c r="E2380">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2381">
+        <v>119</v>
+      </c>
+      <c r="B2381" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C2381">
+        <v>1</v>
+      </c>
+      <c r="D2381">
+        <v>3760</v>
+      </c>
+      <c r="E2381">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
